--- a/Sessin Plan.xlsx
+++ b/Sessin Plan.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="578">
   <si>
     <t>Placement Training Summary Hours</t>
   </si>
@@ -431,13 +431,16 @@
     <t>Brute Force vs Better Approach</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Two Sum (LC 1) - Brute Force Discussion </t>
+    <t>LC 268 Missing Number</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Contains Duplicate (LC 217) </t>
     </r>
     <r>
       <rPr>
@@ -446,17 +449,651 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
+      <t>https://leetcode.com/problems/contains-duplicate/</t>
+    </r>
+  </si>
+  <si>
+    <t>Using Hashing for Optimization</t>
+  </si>
+  <si>
+    <t>LC 1512 Number of Good Pairs</t>
+  </si>
+  <si>
+    <t>Optimization Workshop</t>
+  </si>
+  <si>
+    <t>Data Structure Driven Optimization</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>LC 438 Find All Anagrams in a String+ LC 1365 How Many Numbers Are Smaller Than the Current Number</t>
+    </r>
+  </si>
+  <si>
+    <t>LC 1207 Unique Number of Occurrences</t>
+  </si>
+  <si>
+    <t>Array Internals</t>
+  </si>
+  <si>
+    <t>Memory Layout, Traversal, Insert, Delete, Search, Update</t>
+  </si>
+  <si>
+    <t>Array operations walkthrough</t>
+  </si>
+  <si>
+    <t>Review notes</t>
+  </si>
+  <si>
+    <t>Complexity Analysis</t>
+  </si>
+  <si>
+    <t>O(1) vs O(n), Why Arrays are Fast, Linear Search</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Complexity discussion using LC 1920 </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/build-array-from-permutation/</t>
+    </r>
+  </si>
+  <si>
+    <t>Read problem</t>
+  </si>
+  <si>
+    <t>Two Pointer Pattern</t>
+  </si>
+  <si>
+    <t>Concept, When to Use, Opposite Direction vs Same Direction</t>
+  </si>
+  <si>
+    <t>LC 344 Reverse String</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 167 Two Sum II </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/two-sum-ii-input-array-is-sorted/</t>
+    </r>
+  </si>
+  <si>
+    <t>Array Basics</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 1920 Build Array from Permutation </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/build-array-from-permutation/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 1480 Running Sum of 1D Array </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/running-sum-of-1d-array/</t>
+    </r>
+  </si>
+  <si>
+    <t>Two Pointer</t>
+  </si>
+  <si>
+    <t>LC 977 Squares of a Sorted Array</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 283 Move Zeroes </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/move-zeroes/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 26 Remove Duplicates from Sorted Array </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/remove-duplicates-from-sorted-array/</t>
+    </r>
+  </si>
+  <si>
+    <t>Sliding Window</t>
+  </si>
+  <si>
+    <t>Brute Force vs Sliding Window</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 643 Maximum Average Subarray I </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/maximum-average-subarray-i/</t>
+    </r>
+  </si>
+  <si>
+    <t>Fixed Window</t>
+  </si>
+  <si>
+    <t>Fixed Window Pattern</t>
+  </si>
+  <si>
+    <t>LC 643 walkthrough</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 209 Minimum Size Subarray Sum </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/minimum-size-subarray-sum/</t>
+    </r>
+  </si>
+  <si>
+    <t>Variable Window</t>
+  </si>
+  <si>
+    <t>Dynamic Window Expansion &amp; Shrinking</t>
+  </si>
+  <si>
+    <t>LC 209 walkthrough</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 1456 Maximum Number of Vowels in a Substring </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/maximum-number-of-vowels-in-a-substring-of-given-length/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 3 Longest Substring Without Repeating Characters </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/longest-substring-without-repeating-characters/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 424 Longest Repeating Character Replacement </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/longest-repeating-character-replacement/</t>
+    </r>
+  </si>
+  <si>
+    <t>Prefix Sum</t>
+  </si>
+  <si>
+    <t>Prefix Array Construction, Range Queries</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 303 Range Sum Query Immutable </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/range-sum-query-immutable/</t>
+    </r>
+  </si>
+  <si>
+    <t>Kadane's Algorithm</t>
+  </si>
+  <si>
+    <t>Maximum Subarray Optimization</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 53 Maximum Subarray </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/maximum-subarray/</t>
+    </r>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <t>Prefix Sum vs Sliding Window vs Kadane</t>
+  </si>
+  <si>
+    <t>Compare patterns and selection strategy</t>
+  </si>
+  <si>
+    <t>Pattern worksheet</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 560 Subarray Sum Equals K </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/subarray-sum-equals-k/</t>
+    </r>
+  </si>
+  <si>
+    <t>Kadane</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 152 Maximum Product Subarray </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/maximum-product-subarray/</t>
+    </r>
+  </si>
+  <si>
+    <t>Mixed Array Patterns</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 121 Best Time to Buy and Sell Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/best-time-to-buy-and-sell-stock/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 15 3Sum </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/3sum/</t>
+    </r>
+  </si>
+  <si>
+    <t>Strings Fundamentals</t>
+  </si>
+  <si>
+    <t>Traversal, Indexing, Slicing, String Immutability, Common Operations</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 344 Reverse String </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/reverse-string/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review String Operations</t>
+  </si>
+  <si>
+    <t>String Patterns</t>
+  </si>
+  <si>
+    <t>Palindrome, Character Frequency, String Comparison</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 125 Valid Palindrome </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/valid-palindrome/</t>
+    </r>
+  </si>
+  <si>
+    <t>Read LC 242</t>
+  </si>
+  <si>
+    <t>Hashing Introduction</t>
+  </si>
+  <si>
+    <t>Why Hashing Exists, Hash Function, Buckets, Collision, HashMap, HashSet</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 242 Valid Anagram </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/valid-anagram/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review HashMap Basics</t>
+  </si>
+  <si>
+    <t>String Basics</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 557 Reverse Words in a String III </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/reverse-words-in-a-string-iii/</t>
+    </r>
+  </si>
+  <si>
+    <t>Palindrome Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 680 Valid Palindrome II </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/valid-palindrome-ii/</t>
+    </r>
+  </si>
+  <si>
+    <t>HashMap Frequency Count</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 383 Ransom Note </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/ransom-note/</t>
+    </r>
+  </si>
+  <si>
+    <t>HashMap Internals</t>
+  </si>
+  <si>
+    <t>Key-Value Storage, Lookup Optimization, Complexity Analysis</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 1 Two Sum </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
       <t>https://leetcode.com/problems/two-sum/</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Contains Duplicate (LC 217) </t>
+    <t>Review HashMap Operations</t>
+  </si>
+  <si>
+    <t>HashSet Internals</t>
+  </si>
+  <si>
+    <t>Unique Elements, Duplicate Detection, Membership Testing</t>
+  </si>
+  <si>
+    <t>LC 128 Longest Consecutive Sequence</t>
+  </si>
+  <si>
+    <t>Read LC 49</t>
+  </si>
+  <si>
+    <t>Frequency Map Pattern, Grouping Pattern, Lookup Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 49 Group Anagrams </t>
     </r>
     <r>
       <rPr>
@@ -465,20 +1102,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/contains-duplicate/</t>
-    </r>
-  </si>
-  <si>
-    <t>Using Hashing for Optimization</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Valid Anagram (LC 242) </t>
+      <t>https://leetcode.com/problems/group-anagrams/</t>
+    </r>
+  </si>
+  <si>
+    <t>Pattern Notes</t>
+  </si>
+  <si>
+    <t>HashMap Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 169 Majority Element </t>
     </r>
     <r>
       <rPr>
@@ -487,23 +1127,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/valid-anagram/</t>
-    </r>
-  </si>
-  <si>
-    <t>Optimization Workshop</t>
-  </si>
-  <si>
-    <t>Data Structure Driven Optimization</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Valid Anagram (LC 242) </t>
+      <t>https://leetcode.com/problems/majority-element/</t>
+    </r>
+  </si>
+  <si>
+    <t>HashSet Pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LC 771 Jewels and Stones </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 349 Intersection of Two Arrays </t>
     </r>
     <r>
       <rPr>
@@ -512,15 +1152,53 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/valid-anagram/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> + Two Sum Optimized </t>
+      <t>https://leetcode.com/problems/intersection-of-two-arrays/</t>
+    </r>
+  </si>
+  <si>
+    <t>Frequency &amp; Grouping Pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LC 451 Sort Characters by Frequency </t>
+  </si>
+  <si>
+    <t>Linked List Fundamentals</t>
+  </si>
+  <si>
+    <t>Arrays vs Linked Lists, Node Structure, Memory Representation, Traversal</t>
+  </si>
+  <si>
+    <t>Build a Node class and visualize links using Excalidraw</t>
+  </si>
+  <si>
+    <t>Review Linked List Notes</t>
+  </si>
+  <si>
+    <t>Linked List Operations</t>
+  </si>
+  <si>
+    <t>Insert, Delete, Search, Traverse, Complexity Analysis</t>
+  </si>
+  <si>
+    <t>Implement basic Linked List operations</t>
+  </si>
+  <si>
+    <t>Read LC 206</t>
+  </si>
+  <si>
+    <t>Fast &amp; Slow Pointer Pattern</t>
+  </si>
+  <si>
+    <t>Why Fast-Slow Pointer Exists, Cycle Detection, Middle Node Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 876 Middle of the Linked List </t>
     </r>
     <r>
       <rPr>
@@ -529,17 +1207,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/two-sum/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Majority Element (LC 169) </t>
+      <t>https://leetcode.com/problems/middle-of-the-linked-list/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Pattern Notes</t>
+  </si>
+  <si>
+    <t>Linked List Basics</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 206 Reverse Linked List </t>
     </r>
     <r>
       <rPr>
@@ -548,35 +1232,17 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/majority-element/</t>
-    </r>
-  </si>
-  <si>
-    <t>Array Internals</t>
-  </si>
-  <si>
-    <t>Memory Layout, Traversal, Insert, Delete, Search, Update</t>
-  </si>
-  <si>
-    <t>Array operations walkthrough</t>
-  </si>
-  <si>
-    <t>Review notes</t>
-  </si>
-  <si>
-    <t>Complexity Analysis</t>
-  </si>
-  <si>
-    <t>O(1) vs O(n), Why Arrays are Fast, Linear Search</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Complexity discussion using LC 1920 </t>
+      <t>https://leetcode.com/problems/reverse-linked-list/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 21 Merge Two Sorted Lists </t>
     </r>
     <r>
       <rPr>
@@ -585,26 +1251,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/build-array-from-permutation/</t>
-    </r>
-  </si>
-  <si>
-    <t>Read problem</t>
-  </si>
-  <si>
-    <t>Two Pointer Pattern</t>
-  </si>
-  <si>
-    <t>Concept, When to Use, Opposite Direction vs Same Direction</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 125 Valid Palindrome </t>
+      <t>https://leetcode.com/problems/merge-two-sorted-lists/</t>
+    </r>
+  </si>
+  <si>
+    <t>Fast &amp; Slow Pointer</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 141 Linked List Cycle </t>
     </r>
     <r>
       <rPr>
@@ -613,17 +1273,17 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/valid-palindrome/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 167 Two Sum II </t>
+      <t>https://leetcode.com/problems/linked-list-cycle/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 141 Linked List Cycle </t>
     </r>
     <r>
       <rPr>
@@ -632,20 +1292,25 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/two-sum-ii-input-array-is-sorted/</t>
-    </r>
-  </si>
-  <si>
-    <t>Array Basics</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 1920 Build Array from Permutation </t>
+      <t>https://leetcode.com/problems/linked-list-cycle/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> + Discussion of Fast-Slow Pointer Pattern</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 234 Palindrome Linked List </t>
     </r>
     <r>
       <rPr>
@@ -654,17 +1319,47 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/build-array-from-permutation/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 1480 Running Sum of 1D Array </t>
+      <t>https://leetcode.com/problems/palindrome-linked-list/</t>
+    </r>
+  </si>
+  <si>
+    <t>Stack Fundamentals</t>
+  </si>
+  <si>
+    <t>LIFO Principle, Stack Representation, Real-World Examples, Stack using List</t>
+  </si>
+  <si>
+    <t>Implement push(), pop(), peek(), size(), isEmpty()</t>
+  </si>
+  <si>
+    <t>Review Stack Operations</t>
+  </si>
+  <si>
+    <t>Stack Operations &amp; Complexity</t>
+  </si>
+  <si>
+    <t>Push, Pop, Peek, Underflow, Complexity Analysis, Stack vs Queue</t>
+  </si>
+  <si>
+    <t>Implement Stack from Scratch</t>
+  </si>
+  <si>
+    <t>Read LC 20</t>
+  </si>
+  <si>
+    <t>Monotonic Stack Introduction</t>
+  </si>
+  <si>
+    <t>Why Monotonic Stack Exists, Next Greater Element Pattern, Stack-based Optimization</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 496 Next Greater Element I </t>
     </r>
     <r>
       <rPr>
@@ -673,20 +1368,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/running-sum-of-1d-array/</t>
-    </r>
-  </si>
-  <si>
-    <t>Two Pointer</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 283 Move Zeroes </t>
+      <t>https://leetcode.com/problems/next-greater-element-i/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Monotonic Stack Notes</t>
+  </si>
+  <si>
+    <t>Basic Stack Applications</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 20 Valid Parentheses </t>
     </r>
     <r>
       <rPr>
@@ -695,17 +1393,17 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/move-zeroes/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 26 Remove Duplicates from Sorted Array </t>
+      <t>https://leetcode.com/problems/valid-parentheses/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 682 Baseball Game </t>
     </r>
     <r>
       <rPr>
@@ -714,23 +1412,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/remove-duplicates-from-sorted-array/</t>
-    </r>
-  </si>
-  <si>
-    <t>Sliding Window</t>
-  </si>
-  <si>
-    <t>Brute Force vs Sliding Window</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 643 Maximum Average Subarray I </t>
+      <t>https://leetcode.com/problems/baseball-game/</t>
+    </r>
+  </si>
+  <si>
+    <t>Monotonic Stack Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 739 Daily Temperatures </t>
     </r>
     <r>
       <rPr>
@@ -739,26 +1434,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/maximum-average-subarray-i/</t>
-    </r>
-  </si>
-  <si>
-    <t>Fixed Window</t>
-  </si>
-  <si>
-    <t>Fixed Window Pattern</t>
-  </si>
-  <si>
-    <t>LC 643 walkthrough</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 209 Minimum Size Subarray Sum </t>
+      <t>https://leetcode.com/problems/daily-temperatures/</t>
+    </r>
+  </si>
+  <si>
+    <t>Advanced Stack Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 84 Largest Rectangle in Histogram </t>
     </r>
     <r>
       <rPr>
@@ -767,26 +1456,47 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/minimum-size-subarray-sum/</t>
-    </r>
-  </si>
-  <si>
-    <t>Variable Window</t>
-  </si>
-  <si>
-    <t>Dynamic Window Expansion &amp; Shrinking</t>
-  </si>
-  <si>
-    <t>LC 209 walkthrough</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 1456 Maximum Number of Vowels in a Substring </t>
+      <t>https://leetcode.com/problems/largest-rectangle-in-histogram/</t>
+    </r>
+  </si>
+  <si>
+    <t>Queue Fundamentals</t>
+  </si>
+  <si>
+    <t>FIFO Principle, Queue Representation, Real-world Examples, Queue using List &amp; Deque</t>
+  </si>
+  <si>
+    <t>Implement enqueue(), dequeue(), front(), rear()</t>
+  </si>
+  <si>
+    <t>Review Queue Operations</t>
+  </si>
+  <si>
+    <t>Queue Operations &amp; Complexity</t>
+  </si>
+  <si>
+    <t>Enqueue, Dequeue, Complexity Analysis, Circular Queue, Queue vs Stack</t>
+  </si>
+  <si>
+    <t>Implement Queue from Scratch</t>
+  </si>
+  <si>
+    <t>Read LC 933</t>
+  </si>
+  <si>
+    <t>Deque &amp; BFS Introduction</t>
+  </si>
+  <si>
+    <t>Double Ended Queue, Why Deque Exists, Queue Applications, BFS Foundation</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 933 Number of Recent Calls </t>
     </r>
     <r>
       <rPr>
@@ -795,17 +1505,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/maximum-number-of-vowels-in-a-substring-of-given-length/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 3 Longest Substring Without Repeating Characters </t>
+      <t>https://leetcode.com/problems/number-of-recent-calls/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review BFS Notes</t>
+  </si>
+  <si>
+    <t>Queue Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 225 Implement Stack using Queues </t>
     </r>
     <r>
       <rPr>
@@ -814,17 +1530,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/longest-substring-without-repeating-characters/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 424 Longest Repeating Character Replacement </t>
+      <t>https://leetcode.com/problems/implement-stack-using-queues/</t>
+    </r>
+  </si>
+  <si>
+    <t>Deque Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 239 Sliding Window Maximum </t>
     </r>
     <r>
       <rPr>
@@ -833,23 +1552,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/longest-repeating-character-replacement/</t>
-    </r>
-  </si>
-  <si>
-    <t>Prefix Sum</t>
-  </si>
-  <si>
-    <t>Prefix Array Construction, Range Queries</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 303 Range Sum Query Immutable </t>
+      <t>https://leetcode.com/problems/sliding-window-maximum/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Deque Solution</t>
+  </si>
+  <si>
+    <t>Queue + BFS Foundation</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 649 Dota2 Senate </t>
     </r>
     <r>
       <rPr>
@@ -858,23 +1577,38 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/range-sum-query-immutable/</t>
-    </r>
-  </si>
-  <si>
-    <t>Kadane's Algorithm</t>
-  </si>
-  <si>
-    <t>Maximum Subarray Optimization</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 53 Maximum Subarray </t>
+      <t>https://leetcode.com/problems/dota2-senate/</t>
+    </r>
+  </si>
+  <si>
+    <t>Prepare for Recursion Module</t>
+  </si>
+  <si>
+    <t>Recursion Fundamentals</t>
+  </si>
+  <si>
+    <t>What is Recursion, Base Case, Recursive Case, Call Stack Visualization</t>
+  </si>
+  <si>
+    <t>Dry run recursion using Excalidraw</t>
+  </si>
+  <si>
+    <t>Review Recursion Notes</t>
+  </si>
+  <si>
+    <t>Recursive Thinking</t>
+  </si>
+  <si>
+    <t>How to Think Recursively, Faith &amp; Trust Principle, Recursive Tree</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 509 Fibonacci Number </t>
     </r>
     <r>
       <rPr>
@@ -883,29 +1617,35 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/maximum-subarray/</t>
-    </r>
-  </si>
-  <si>
-    <t>Pattern Recognition</t>
-  </si>
-  <si>
-    <t>Prefix Sum vs Sliding Window vs Kadane</t>
-  </si>
-  <si>
-    <t>Compare patterns and selection strategy</t>
-  </si>
-  <si>
-    <t>Pattern worksheet</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 560 Subarray Sum Equals K </t>
+      <t>https://leetcode.com/problems/fibonacci-number/</t>
+    </r>
+  </si>
+  <si>
+    <t>Read LC 70</t>
+  </si>
+  <si>
+    <t>Multiple Recursive Calls</t>
+  </si>
+  <si>
+    <t>Recursion Tree, Time Complexity of Recursion, Exponential Growth</t>
+  </si>
+  <si>
+    <t>LC 779 K-th Symbol in Grammar</t>
+  </si>
+  <si>
+    <t>Review Recursion Tree</t>
+  </si>
+  <si>
+    <t>Basic Recursion</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 231 Power of Two </t>
     </r>
     <r>
       <rPr>
@@ -914,20 +1654,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/subarray-sum-equals-k/</t>
-    </r>
-  </si>
-  <si>
-    <t>Kadane</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 152 Maximum Product Subarray </t>
+      <t>https://leetcode.com/problems/power-of-two/</t>
+    </r>
+  </si>
+  <si>
+    <t>Recursive Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 50 Pow(x,n) </t>
     </r>
     <r>
       <rPr>
@@ -936,20 +1676,41 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/maximum-product-subarray/</t>
-    </r>
-  </si>
-  <si>
-    <t>Mixed Array Patterns</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 121 Best Time to Buy and Sell Stock </t>
+      <t>https://leetcode.com/problems/powx-n/</t>
+    </r>
+  </si>
+  <si>
+    <t>LC 344 Reverse String using recursion or LC 1823 Find the Winner of the Circular Game</t>
+  </si>
+  <si>
+    <t>Review Recursion Problems</t>
+  </si>
+  <si>
+    <t>Backtracking Fundamentals</t>
+  </si>
+  <si>
+    <t>Decision Tree, Choose-Explore-Unchoose, State Space Search</t>
+  </si>
+  <si>
+    <t>Visualize decision tree using Excalidraw</t>
+  </si>
+  <si>
+    <t>Review Backtracking Notes</t>
+  </si>
+  <si>
+    <t>Pick / Not Pick Pattern</t>
+  </si>
+  <si>
+    <t>Subset Generation Pattern, Decision Tree Visualization</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 78 Subsets </t>
     </r>
     <r>
       <rPr>
@@ -958,17 +1719,26 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/best-time-to-buy-and-sell-stock/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 15 3Sum </t>
+      <t>https://leetcode.com/problems/subsets/</t>
+    </r>
+  </si>
+  <si>
+    <t>Read LC 39</t>
+  </si>
+  <si>
+    <t>Backtracking Patterns</t>
+  </si>
+  <si>
+    <t>Subsets, Combinations, Permutations, Complexity Discussion</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 39 Combination Sum </t>
     </r>
     <r>
       <rPr>
@@ -977,23 +1747,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/3sum/</t>
-    </r>
-  </si>
-  <si>
-    <t>Strings Fundamentals</t>
-  </si>
-  <si>
-    <t>Traversal, Indexing, Slicing, String Immutability, Common Operations</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 344 Reverse String </t>
+      <t>https://leetcode.com/problems/combination-sum/</t>
+    </r>
+  </si>
+  <si>
+    <t>Subset Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 90 Subsets II </t>
     </r>
     <r>
       <rPr>
@@ -1002,35 +1769,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/reverse-string/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review String Operations</t>
-  </si>
-  <si>
-    <t>String Patterns</t>
-  </si>
-  <si>
-    <t>Palindrome, Character Frequency, String Comparison</t>
-  </si>
-  <si>
-    <t>Read LC 242</t>
-  </si>
-  <si>
-    <t>Hashing Introduction</t>
-  </si>
-  <si>
-    <t>Why Hashing Exists, Hash Function, Buckets, Collision, HashMap, HashSet</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 242 Valid Anagram </t>
+      <t>https://leetcode.com/problems/subsets-ii/</t>
+    </r>
+  </si>
+  <si>
+    <t>Combination Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 77 Combinations </t>
     </r>
     <r>
       <rPr>
@@ -1039,23 +1791,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/valid-anagram/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review HashMap Basics</t>
-  </si>
-  <si>
-    <t>String Basics</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 557 Reverse Words in a String III </t>
+      <t>https://leetcode.com/problems/combinations/</t>
+    </r>
+  </si>
+  <si>
+    <t>Permutation Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 46 Permutations </t>
     </r>
     <r>
       <rPr>
@@ -1064,20 +1813,17 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/reverse-words-in-a-string-iii/</t>
-    </r>
-  </si>
-  <si>
-    <t>Palindrome Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 680 Valid Palindrome II </t>
+      <t>https://leetcode.com/problems/permutations/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 131 Palindrome Partitioning </t>
     </r>
     <r>
       <rPr>
@@ -1086,20 +1832,35 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/valid-palindrome-ii/</t>
-    </r>
-  </si>
-  <si>
-    <t>HashMap Frequency Count</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 383 Ransom Note </t>
+      <t>https://leetcode.com/problems/palindrome-partitioning/</t>
+    </r>
+  </si>
+  <si>
+    <t>Tree Fundamentals</t>
+  </si>
+  <si>
+    <t>Tree Terminology, Root, Parent, Child, Leaf, Height, Depth, Binary Tree Structure</t>
+  </si>
+  <si>
+    <t>Build Tree Node Class using Python</t>
+  </si>
+  <si>
+    <t>Review Tree Terminology</t>
+  </si>
+  <si>
+    <t>Tree Traversals</t>
+  </si>
+  <si>
+    <t>DFS, Preorder, Inorder, Postorder, Recursive Traversals</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 144 Binary Tree Preorder Traversal </t>
     </r>
     <r>
       <rPr>
@@ -1108,23 +1869,26 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/ransom-note/</t>
-    </r>
-  </si>
-  <si>
-    <t>HashMap Internals</t>
-  </si>
-  <si>
-    <t>Key-Value Storage, Lookup Optimization, Complexity Analysis</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 1 Two Sum </t>
+      <t>https://leetcode.com/problems/binary-tree-preorder-traversal/</t>
+    </r>
+  </si>
+  <si>
+    <t>Read LC 94</t>
+  </si>
+  <si>
+    <t>BFS Traversal</t>
+  </si>
+  <si>
+    <t>Level Order Traversal, Queue Usage in Trees</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 102 Binary Tree Level Order Traversal </t>
     </r>
     <r>
       <rPr>
@@ -1133,26 +1897,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/two-sum/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review HashMap Operations</t>
-  </si>
-  <si>
-    <t>HashSet Internals</t>
-  </si>
-  <si>
-    <t>Unique Elements, Duplicate Detection, Membership Testing</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 217 Contains Duplicate </t>
+      <t>https://leetcode.com/problems/binary-tree-level-order-traversal/</t>
+    </r>
+  </si>
+  <si>
+    <t>DFS Traversals</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 94 Binary Tree Inorder Traversal </t>
     </r>
     <r>
       <rPr>
@@ -1161,23 +1919,17 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/contains-duplicate/</t>
-    </r>
-  </si>
-  <si>
-    <t>Read LC 49</t>
-  </si>
-  <si>
-    <t>Frequency Map Pattern, Grouping Pattern, Lookup Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 49 Group Anagrams </t>
+      <t>https://leetcode.com/problems/binary-tree-inorder-traversal/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 145 Binary Tree Postorder Traversal </t>
     </r>
     <r>
       <rPr>
@@ -1186,23 +1938,17 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/group-anagrams/</t>
-    </r>
-  </si>
-  <si>
-    <t>Pattern Notes</t>
-  </si>
-  <si>
-    <t>HashMap Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 169 Majority Element </t>
+      <t>https://leetcode.com/problems/binary-tree-postorder-traversal/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 103 Binary Tree Zigzag Level Order Traversal </t>
     </r>
     <r>
       <rPr>
@@ -1211,20 +1957,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/majority-element/</t>
-    </r>
-  </si>
-  <si>
-    <t>HashSet Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 349 Intersection of Two Arrays </t>
+      <t>https://leetcode.com/problems/binary-tree-zigzag-level-order-traversal/</t>
+    </r>
+  </si>
+  <si>
+    <t>Tree Interview Patterns</t>
+  </si>
+  <si>
+    <t>Height, Depth, Diameter, Recursive Tree Problems</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 104 Maximum Depth of Binary Tree </t>
     </r>
     <r>
       <rPr>
@@ -1233,11 +1982,481 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/intersection-of-two-arrays/</t>
-    </r>
-  </si>
-  <si>
-    <t>Frequency &amp; Grouping Pattern</t>
+      <t>https://leetcode.com/problems/maximum-depth-of-binary-tree/</t>
+    </r>
+  </si>
+  <si>
+    <t>Read LC 543</t>
+  </si>
+  <si>
+    <t>Binary Search Tree</t>
+  </si>
+  <si>
+    <t>BST Properties, Search, Insert, Complexity Analysis</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 700 Search in a Binary Search Tree </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/search-in-a-binary-search-tree/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review BST Notes</t>
+  </si>
+  <si>
+    <t>BST Patterns</t>
+  </si>
+  <si>
+    <t>Validation, LCA, Search Space Optimization</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 98 Validate Binary Search Tree </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/validate-binary-search-tree/</t>
+    </r>
+  </si>
+  <si>
+    <t>Read LC 235</t>
+  </si>
+  <si>
+    <t>Height &amp; Diameter Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 543 Diameter of Binary Tree </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/diameter-of-binary-tree/</t>
+    </r>
+  </si>
+  <si>
+    <t>BST Pattern</t>
+  </si>
+  <si>
+    <t>LCA Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 235 Lowest Common Ancestor of a BST </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/lowest-common-ancestor-of-a-binary-search-tree/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 112 Path Sum </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/path-sum/</t>
+    </r>
+  </si>
+  <si>
+    <t>Graph Fundamentals</t>
+  </si>
+  <si>
+    <t>Vertices, Edges, Directed vs Undirected Graphs, Weighted vs Unweighted Graphs</t>
+  </si>
+  <si>
+    <t>Visualize graphs using Excalidraw</t>
+  </si>
+  <si>
+    <t>Review Graph Terminology</t>
+  </si>
+  <si>
+    <t>Graph Representation</t>
+  </si>
+  <si>
+    <t>Adjacency Matrix, Adjacency List, Complexity Analysis</t>
+  </si>
+  <si>
+    <t>Build Graph Representation in Python</t>
+  </si>
+  <si>
+    <t>Read LC 1971</t>
+  </si>
+  <si>
+    <t>DFS &amp; BFS in Graphs</t>
+  </si>
+  <si>
+    <t>Revisiting DFS and BFS, Traversal Strategies, Visited Array Concept</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 1971 Find if Path Exists in Graph </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/find-if-path-exists-in-graph/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review DFS/BFS Notes</t>
+  </si>
+  <si>
+    <t>Graph Traversal</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 841 Keys and Rooms </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/keys-and-rooms/</t>
+    </r>
+  </si>
+  <si>
+    <t>DFS Pattern</t>
+  </si>
+  <si>
+    <t>Review DFS Solution</t>
+  </si>
+  <si>
+    <t>Connected Components</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 547 Number of Provinces </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/number-of-provinces/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Connected Components Pattern</t>
+  </si>
+  <si>
+    <t>Connected Components Pattern</t>
+  </si>
+  <si>
+    <t>DFS/BFS Applications, Island-Type Problems</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 200 Number of Islands </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/number-of-islands/</t>
+    </r>
+  </si>
+  <si>
+    <t>Read LC 994</t>
+  </si>
+  <si>
+    <t>Multi-Source BFS</t>
+  </si>
+  <si>
+    <t>BFS from Multiple Sources, Queue Expansion Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 994 Rotten Oranges </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/rotting-oranges/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Multi-Source BFS</t>
+  </si>
+  <si>
+    <t>Topological Sort Introduction</t>
+  </si>
+  <si>
+    <t>Dependency Graphs, DAG, Course Scheduling Concept</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 207 Course Schedule </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/course-schedule/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Topological Sort Notes</t>
+  </si>
+  <si>
+    <t>Island Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 695 Max Area of Island </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/max-area-of-island/</t>
+    </r>
+  </si>
+  <si>
+    <t>Multi-Source BFS Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 542 01 Matrix </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/01-matrix/</t>
+    </r>
+  </si>
+  <si>
+    <t>Topological Sort Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 210 Course Schedule II </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/course-schedule-ii/</t>
+    </r>
+  </si>
+  <si>
+    <t>Heap Fundamentals</t>
+  </si>
+  <si>
+    <t>Complete Binary Tree, Min Heap, Max Heap, Heap Property, Heap Representation</t>
+  </si>
+  <si>
+    <t>Visualize Heap using Excalidraw</t>
+  </si>
+  <si>
+    <t>Review Heap Terminology</t>
+  </si>
+  <si>
+    <t>Heap Operations</t>
+  </si>
+  <si>
+    <t>Insert, Delete, Heapify, Complexity Analysis, Priority Queue</t>
+  </si>
+  <si>
+    <t>Implement Min Heap using Python heapq</t>
+  </si>
+  <si>
+    <t>Read LC 215</t>
+  </si>
+  <si>
+    <t>Top-K Pattern</t>
+  </si>
+  <si>
+    <t>Why Heap is Better than Sorting, K Largest / K Smallest Problems, Priority Queue Thinking</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 215 Kth Largest Element in an Array </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/kth-largest-element-in-an-array/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Top-K Pattern Notes</t>
+  </si>
+  <si>
+    <t>Heap Basics</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 703 Kth Largest Element in a Stream </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/kth-largest-element-in-a-stream/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 1046 Last Stone Weight </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>https://leetcode.com/problems/last-stone-weight/</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1259,43 +2478,16 @@
     </r>
   </si>
   <si>
-    <t>Linked List Fundamentals</t>
-  </si>
-  <si>
-    <t>Arrays vs Linked Lists, Node Structure, Memory Representation, Traversal</t>
-  </si>
-  <si>
-    <t>Build a Node class and visualize links using Excalidraw</t>
-  </si>
-  <si>
-    <t>Review Linked List Notes</t>
-  </si>
-  <si>
-    <t>Linked List Operations</t>
-  </si>
-  <si>
-    <t>Insert, Delete, Search, Traverse, Complexity Analysis</t>
-  </si>
-  <si>
-    <t>Implement basic Linked List operations</t>
-  </si>
-  <si>
-    <t>Read LC 206</t>
-  </si>
-  <si>
-    <t>Fast &amp; Slow Pointer Pattern</t>
-  </si>
-  <si>
-    <t>Why Fast-Slow Pointer Exists, Cycle Detection, Middle Node Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 876 Middle of the Linked List </t>
+    <t>Priority Queue Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 973 K Closest Points to Origin </t>
     </r>
     <r>
       <rPr>
@@ -1304,23 +2496,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/middle-of-the-linked-list/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Pattern Notes</t>
-  </si>
-  <si>
-    <t>Linked List Basics</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 206 Reverse Linked List </t>
+      <t>https://leetcode.com/problems/k-closest-points-to-origin/</t>
+    </r>
+  </si>
+  <si>
+    <t>Binary Search Fundamentals</t>
+  </si>
+  <si>
+    <t>Linear Search vs Binary Search, Prerequisites, Sorted Array Concept, Search Space Reduction</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 704 Binary Search </t>
     </r>
     <r>
       <rPr>
@@ -1329,17 +2521,38 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/reverse-linked-list/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 21 Merge Two Sorted Lists </t>
+      <t>https://leetcode.com/problems/binary-search/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Binary Search Notes</t>
+  </si>
+  <si>
+    <t>Binary Search Implementation</t>
+  </si>
+  <si>
+    <t>Iterative Binary Search, Recursive Binary Search, Mid Calculation, Complexity Analysis</t>
+  </si>
+  <si>
+    <t>Implement Binary Search from Scratch</t>
+  </si>
+  <si>
+    <t>Read LC 35</t>
+  </si>
+  <si>
+    <t>Binary Search on Answer</t>
+  </si>
+  <si>
+    <t>Monotonic Functions, Search Space Thinking, Optimization Problems</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 875 Koko Eating Bananas </t>
     </r>
     <r>
       <rPr>
@@ -1348,20 +2561,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/merge-two-sorted-lists/</t>
-    </r>
-  </si>
-  <si>
-    <t>Fast &amp; Slow Pointer</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 141 Linked List Cycle </t>
+      <t>https://leetcode.com/problems/koko-eating-bananas/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Binary Search on Answer Notes</t>
+  </si>
+  <si>
+    <t>Basic Binary Search Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 35 Search Insert Position </t>
     </r>
     <r>
       <rPr>
@@ -1370,17 +2586,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/linked-list-cycle/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 141 Linked List Cycle </t>
+      <t>https://leetcode.com/problems/search-insert-position/</t>
+    </r>
+  </si>
+  <si>
+    <t>Boundary Search Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 34 Find First and Last Position of Element in Sorted Array </t>
     </r>
     <r>
       <rPr>
@@ -1389,25 +2608,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/linked-list-cycle/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> + Discussion of Fast-Slow Pointer Pattern</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 234 Palindrome Linked List </t>
+      <t>https://leetcode.com/problems/find-first-and-last-position-of-element-in-sorted-array/</t>
+    </r>
+  </si>
+  <si>
+    <t>Binary Search on Answer Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 1011 Capacity To Ship Packages Within D Days </t>
     </r>
     <r>
       <rPr>
@@ -1416,47 +2630,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/palindrome-linked-list/</t>
-    </r>
-  </si>
-  <si>
-    <t>Stack Fundamentals</t>
-  </si>
-  <si>
-    <t>LIFO Principle, Stack Representation, Real-World Examples, Stack using List</t>
-  </si>
-  <si>
-    <t>Implement push(), pop(), peek(), size(), isEmpty()</t>
-  </si>
-  <si>
-    <t>Review Stack Operations</t>
-  </si>
-  <si>
-    <t>Stack Operations &amp; Complexity</t>
-  </si>
-  <si>
-    <t>Push, Pop, Peek, Underflow, Complexity Analysis, Stack vs Queue</t>
-  </si>
-  <si>
-    <t>Implement Stack from Scratch</t>
-  </si>
-  <si>
-    <t>Read LC 20</t>
-  </si>
-  <si>
-    <t>Monotonic Stack Introduction</t>
-  </si>
-  <si>
-    <t>Why Monotonic Stack Exists, Next Greater Element Pattern, Stack-based Optimization</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 496 Next Greater Element I </t>
+      <t>https://leetcode.com/problems/capacity-to-ship-packages-within-d-days/</t>
+    </r>
+  </si>
+  <si>
+    <t>Greedy Fundamentals</t>
+  </si>
+  <si>
+    <t>What is Greedy, Local Optimum vs Global Optimum, Greedy Choice Property, When Greedy Works</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 455 Assign Cookies </t>
     </r>
     <r>
       <rPr>
@@ -1465,23 +2655,26 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/next-greater-element-i/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Monotonic Stack Notes</t>
-  </si>
-  <si>
-    <t>Basic Stack Applications</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 20 Valid Parentheses </t>
+      <t>https://leetcode.com/problems/assign-cookies/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Greedy Notes</t>
+  </si>
+  <si>
+    <t>Greedy Strategy</t>
+  </si>
+  <si>
+    <t>Sorting + Greedy, Interval Thinking, Decision Making</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 605 Can Place Flowers </t>
     </r>
     <r>
       <rPr>
@@ -1490,17 +2683,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/valid-parentheses/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 682 Baseball Game </t>
+      <t>https://leetcode.com/problems/can-place-flowers/</t>
+    </r>
+  </si>
+  <si>
+    <t>Read LC 860</t>
+  </si>
+  <si>
+    <t>How to Identify Greedy Problems, Greedy vs DP, Common Greedy Patterns</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 860 Lemonade Change </t>
     </r>
     <r>
       <rPr>
@@ -1509,20 +2708,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/baseball-game/</t>
-    </r>
-  </si>
-  <si>
-    <t>Monotonic Stack Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 739 Daily Temperatures </t>
+      <t>https://leetcode.com/problems/lemonade-change/</t>
+    </r>
+  </si>
+  <si>
+    <t>Resource Allocation Pattern</t>
+  </si>
+  <si>
+    <t>Simulation + Greedy Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 55 Jump Game </t>
     </r>
     <r>
       <rPr>
@@ -1531,20 +2733,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/daily-temperatures/</t>
-    </r>
-  </si>
-  <si>
-    <t>Advanced Stack Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 84 Largest Rectangle in Histogram </t>
+      <t>https://leetcode.com/problems/jump-game/</t>
+    </r>
+  </si>
+  <si>
+    <t>Reachability &amp; Interval Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 452 Minimum Number of Arrows to Burst Balloons </t>
     </r>
     <r>
       <rPr>
@@ -1553,47 +2755,41 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/largest-rectangle-in-histogram/</t>
-    </r>
-  </si>
-  <si>
-    <t>Queue Fundamentals</t>
-  </si>
-  <si>
-    <t>FIFO Principle, Queue Representation, Real-world Examples, Queue using List &amp; Deque</t>
-  </si>
-  <si>
-    <t>Implement enqueue(), dequeue(), front(), rear()</t>
-  </si>
-  <si>
-    <t>Review Queue Operations</t>
-  </si>
-  <si>
-    <t>Queue Operations &amp; Complexity</t>
-  </si>
-  <si>
-    <t>Enqueue, Dequeue, Complexity Analysis, Circular Queue, Queue vs Stack</t>
-  </si>
-  <si>
-    <t>Implement Queue from Scratch</t>
-  </si>
-  <si>
-    <t>Read LC 933</t>
-  </si>
-  <si>
-    <t>Deque &amp; BFS Introduction</t>
-  </si>
-  <si>
-    <t>Double Ended Queue, Why Deque Exists, Queue Applications, BFS Foundation</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 933 Number of Recent Calls </t>
+      <t>https://leetcode.com/problems/minimum-number-of-arrows-to-burst-balloons/</t>
+    </r>
+  </si>
+  <si>
+    <t>Why DP Exists</t>
+  </si>
+  <si>
+    <t>Recursion Review, Overlapping Subproblems, Optimal Substructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LC 118 Pascal's Triangle</t>
+  </si>
+  <si>
+    <t>Memoization</t>
+  </si>
+  <si>
+    <t>Top-Down DP, Cache Concept, Avoiding Repeated Computation</t>
+  </si>
+  <si>
+    <t>LC 509 Fibonacci Memoization</t>
+  </si>
+  <si>
+    <t>Tabulation</t>
+  </si>
+  <si>
+    <t>Bottom-Up DP, State Transition, DP Array</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 70 Climbing Stairs </t>
     </r>
     <r>
       <rPr>
@@ -1602,23 +2798,26 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/number-of-recent-calls/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review BFS Notes</t>
-  </si>
-  <si>
-    <t>Queue Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 225 Implement Stack using Queues </t>
+      <t>https://leetcode.com/problems/climbing-stairs/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review DP Notes</t>
+  </si>
+  <si>
+    <t>Fibonacci Pattern</t>
+  </si>
+  <si>
+    <t>LC 1137 N-th Tribonacci</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 1137 N-th Tribonacci Number </t>
     </r>
     <r>
       <rPr>
@@ -1627,20 +2826,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/implement-stack-using-queues/</t>
-    </r>
-  </si>
-  <si>
-    <t>Deque Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 239 Sliding Window Maximum </t>
+      <t>https://leetcode.com/problems/n-th-tribonacci-number/</t>
+    </r>
+  </si>
+  <si>
+    <t>Climbing Stairs Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 746 Min Cost Climbing Stairs </t>
     </r>
     <r>
       <rPr>
@@ -1649,23 +2848,29 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/sliding-window-maximum/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Deque Solution</t>
-  </si>
-  <si>
-    <t>Queue + BFS Foundation</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 649 Dota2 Senate </t>
+      <t>https://leetcode.com/problems/min-cost-climbing-stairs/</t>
+    </r>
+  </si>
+  <si>
+    <t>DP State Recognition</t>
+  </si>
+  <si>
+    <t>DP Revision Worksheet</t>
+  </si>
+  <si>
+    <t>House Robber Pattern</t>
+  </si>
+  <si>
+    <t>State Definition, Decision Making, Include/Exclude</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 198 House Robber </t>
     </r>
     <r>
       <rPr>
@@ -1674,38 +2879,38 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/dota2-senate/</t>
-    </r>
-  </si>
-  <si>
-    <t>Prepare for Recursion Module</t>
-  </si>
-  <si>
-    <t>Recursion Fundamentals</t>
-  </si>
-  <si>
-    <t>What is Recursion, Base Case, Recursive Case, Call Stack Visualization</t>
-  </si>
-  <si>
-    <t>Dry run recursion using Excalidraw</t>
-  </si>
-  <si>
-    <t>Review Recursion Notes</t>
-  </si>
-  <si>
-    <t>Recursive Thinking</t>
-  </si>
-  <si>
-    <t>How to Think Recursively, Faith &amp; Trust Principle, Recursive Tree</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 509 Fibonacci Number </t>
+      <t>https://leetcode.com/problems/house-robber/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review House Robber Pattern</t>
+  </si>
+  <si>
+    <t>DP Optimization</t>
+  </si>
+  <si>
+    <t>Space Optimization, Rolling Variables</t>
+  </si>
+  <si>
+    <t>LC 198 Walkthrough</t>
+  </si>
+  <si>
+    <t>Read LC 213</t>
+  </si>
+  <si>
+    <t>Coin Change Pattern</t>
+  </si>
+  <si>
+    <t>Minimum Coins, State Transition</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 322 Coin Change </t>
     </r>
     <r>
       <rPr>
@@ -1714,26 +2919,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/fibonacci-number/</t>
-    </r>
-  </si>
-  <si>
-    <t>Read LC 70</t>
-  </si>
-  <si>
-    <t>Multiple Recursive Calls</t>
-  </si>
-  <si>
-    <t>Recursion Tree, Time Complexity of Recursion, Exponential Growth</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 70 Climbing Stairs </t>
+      <t>https://leetcode.com/problems/coin-change/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Coin Change Notes</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 213 House Robber II </t>
     </r>
     <r>
       <rPr>
@@ -1742,23 +2941,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/climbing-stairs/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Recursion Tree</t>
-  </si>
-  <si>
-    <t>Basic Recursion</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 231 Power of Two </t>
+      <t>https://leetcode.com/problems/house-robber-ii/</t>
+    </r>
+  </si>
+  <si>
+    <t>Circular DP Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 740 Delete and Earn </t>
     </r>
     <r>
       <rPr>
@@ -1767,20 +2963,17 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/power-of-two/</t>
-    </r>
-  </si>
-  <si>
-    <t>Recursive Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 50 Pow(x,n) </t>
+      <t>https://leetcode.com/problems/delete-and-earn/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 518 Coin Change II </t>
     </r>
     <r>
       <rPr>
@@ -1789,38 +2982,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/powx-n/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Recursion Problems</t>
-  </si>
-  <si>
-    <t>Backtracking Fundamentals</t>
-  </si>
-  <si>
-    <t>Decision Tree, Choose-Explore-Unchoose, State Space Search</t>
-  </si>
-  <si>
-    <t>Visualize decision tree using Excalidraw</t>
-  </si>
-  <si>
-    <t>Review Backtracking Notes</t>
-  </si>
-  <si>
-    <t>Pick / Not Pick Pattern</t>
-  </si>
-  <si>
-    <t>Subset Generation Pattern, Decision Tree Visualization</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 78 Subsets </t>
+      <t>https://leetcode.com/problems/coin-change-ii/</t>
+    </r>
+  </si>
+  <si>
+    <t>Grid DP</t>
+  </si>
+  <si>
+    <t>Rows, Columns, State Transition Matrix</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 62 Unique Paths </t>
     </r>
     <r>
       <rPr>
@@ -1829,26 +3007,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/subsets/</t>
-    </r>
-  </si>
-  <si>
-    <t>Read LC 39</t>
-  </si>
-  <si>
-    <t>Backtracking Patterns</t>
-  </si>
-  <si>
-    <t>Subsets, Combinations, Permutations, Complexity Discussion</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 39 Combination Sum </t>
+      <t>https://leetcode.com/problems/unique-paths/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Grid DP Notes</t>
+  </si>
+  <si>
+    <t>Path-Based Optimization Problems</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 64 Minimum Path Sum </t>
     </r>
     <r>
       <rPr>
@@ -1857,20 +3032,26 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/combination-sum/</t>
-    </r>
-  </si>
-  <si>
-    <t>Subset Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 90 Subsets II </t>
+      <t>https://leetcode.com/problems/minimum-path-sum/</t>
+    </r>
+  </si>
+  <si>
+    <t>Read LC 63</t>
+  </si>
+  <si>
+    <t>Obstacle-Based DP</t>
+  </si>
+  <si>
+    <t>Handling Constraints in DP Grids</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 63 Unique Paths II </t>
     </r>
     <r>
       <rPr>
@@ -1879,20 +3060,26 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/subsets-ii/</t>
-    </r>
-  </si>
-  <si>
-    <t>Combination Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 77 Combinations </t>
+      <t>https://leetcode.com/problems/unique-paths-ii/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review State Transition</t>
+  </si>
+  <si>
+    <t>Unique Paths Pattern</t>
+  </si>
+  <si>
+    <t>Minimum Cost Path Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 931 Minimum Falling Path Sum </t>
     </r>
     <r>
       <rPr>
@@ -1901,20 +3088,32 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/combinations/</t>
-    </r>
-  </si>
-  <si>
-    <t>Permutation Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 46 Permutations </t>
+      <t>https://leetcode.com/problems/minimum-falling-path-sum/</t>
+    </r>
+  </si>
+  <si>
+    <t>Grid DP Pattern Recognition</t>
+  </si>
+  <si>
+    <t>LC 120 Triangle</t>
+  </si>
+  <si>
+    <t>Grid DP Revision</t>
+  </si>
+  <si>
+    <t>Longest Common Subsequence</t>
+  </si>
+  <si>
+    <t>Matching Decisions, 2D DP Table</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 1143 Longest Common Subsequence </t>
     </r>
     <r>
       <rPr>
@@ -1923,17 +3122,26 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/permutations/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 131 Palindrome Partitioning </t>
+      <t>https://leetcode.com/problems/longest-common-subsequence/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review LCS Notes</t>
+  </si>
+  <si>
+    <t>Edit Distance</t>
+  </si>
+  <si>
+    <t>Insert, Delete, Replace Operations</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 72 Edit Distance </t>
     </r>
     <r>
       <rPr>
@@ -1942,35 +3150,26 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/palindrome-partitioning/</t>
-    </r>
-  </si>
-  <si>
-    <t>Tree Fundamentals</t>
-  </si>
-  <si>
-    <t>Tree Terminology, Root, Parent, Child, Leaf, Height, Depth, Binary Tree Structure</t>
-  </si>
-  <si>
-    <t>Build Tree Node Class using Python</t>
-  </si>
-  <si>
-    <t>Review Tree Terminology</t>
-  </si>
-  <si>
-    <t>Tree Traversals</t>
-  </si>
-  <si>
-    <t>DFS, Preorder, Inorder, Postorder, Recursive Traversals</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 144 Binary Tree Preorder Traversal </t>
+      <t>https://leetcode.com/problems/edit-distance/</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Edit Distance</t>
+  </si>
+  <si>
+    <t>Subset DP</t>
+  </si>
+  <si>
+    <t>Target Sum, Partition Problems, Pick/Not Pick Revisited</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 416 Partition Equal Subset Sum </t>
     </r>
     <r>
       <rPr>
@@ -1979,26 +3178,23 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/binary-tree-preorder-traversal/</t>
-    </r>
-  </si>
-  <si>
-    <t>Read LC 94</t>
-  </si>
-  <si>
-    <t>BFS Traversal</t>
-  </si>
-  <si>
-    <t>Level Order Traversal, Queue Usage in Trees</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 102 Binary Tree Level Order Traversal </t>
+      <t>https://leetcode.com/problems/partition-equal-subset-sum/</t>
+    </r>
+  </si>
+  <si>
+    <t>Read LC 494</t>
+  </si>
+  <si>
+    <t>LCS Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 583 Delete Operation for Two Strings </t>
     </r>
     <r>
       <rPr>
@@ -2007,20 +3203,20 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/binary-tree-level-order-traversal/</t>
-    </r>
-  </si>
-  <si>
-    <t>DFS Traversals</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 94 Binary Tree Inorder Traversal </t>
+      <t>https://leetcode.com/problems/delete-operation-for-two-strings/</t>
+    </r>
+  </si>
+  <si>
+    <t>Partition Pattern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">LC 494 Target Sum </t>
     </r>
     <r>
       <rPr>
@@ -2029,1268 +3225,6 @@
         <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>https://leetcode.com/problems/binary-tree-inorder-traversal/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 145 Binary Tree Postorder Traversal </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/binary-tree-postorder-traversal/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 103 Binary Tree Zigzag Level Order Traversal </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/binary-tree-zigzag-level-order-traversal/</t>
-    </r>
-  </si>
-  <si>
-    <t>Tree Interview Patterns</t>
-  </si>
-  <si>
-    <t>Height, Depth, Diameter, Recursive Tree Problems</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 104 Maximum Depth of Binary Tree </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/maximum-depth-of-binary-tree/</t>
-    </r>
-  </si>
-  <si>
-    <t>Read LC 543</t>
-  </si>
-  <si>
-    <t>Binary Search Tree</t>
-  </si>
-  <si>
-    <t>BST Properties, Search, Insert, Complexity Analysis</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 700 Search in a Binary Search Tree </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/search-in-a-binary-search-tree/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review BST Notes</t>
-  </si>
-  <si>
-    <t>BST Patterns</t>
-  </si>
-  <si>
-    <t>Validation, LCA, Search Space Optimization</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 98 Validate Binary Search Tree </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/validate-binary-search-tree/</t>
-    </r>
-  </si>
-  <si>
-    <t>Read LC 235</t>
-  </si>
-  <si>
-    <t>Height &amp; Diameter Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 543 Diameter of Binary Tree </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/diameter-of-binary-tree/</t>
-    </r>
-  </si>
-  <si>
-    <t>BST Pattern</t>
-  </si>
-  <si>
-    <t>LCA Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 235 Lowest Common Ancestor of a BST </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/lowest-common-ancestor-of-a-binary-search-tree/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 112 Path Sum </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/path-sum/</t>
-    </r>
-  </si>
-  <si>
-    <t>Graph Fundamentals</t>
-  </si>
-  <si>
-    <t>Vertices, Edges, Directed vs Undirected Graphs, Weighted vs Unweighted Graphs</t>
-  </si>
-  <si>
-    <t>Visualize graphs using Excalidraw</t>
-  </si>
-  <si>
-    <t>Review Graph Terminology</t>
-  </si>
-  <si>
-    <t>Graph Representation</t>
-  </si>
-  <si>
-    <t>Adjacency Matrix, Adjacency List, Complexity Analysis</t>
-  </si>
-  <si>
-    <t>Build Graph Representation in Python</t>
-  </si>
-  <si>
-    <t>Read LC 1971</t>
-  </si>
-  <si>
-    <t>DFS &amp; BFS in Graphs</t>
-  </si>
-  <si>
-    <t>Revisiting DFS and BFS, Traversal Strategies, Visited Array Concept</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 1971 Find if Path Exists in Graph </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/find-if-path-exists-in-graph/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review DFS/BFS Notes</t>
-  </si>
-  <si>
-    <t>Graph Traversal</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 841 Keys and Rooms </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/keys-and-rooms/</t>
-    </r>
-  </si>
-  <si>
-    <t>DFS Pattern</t>
-  </si>
-  <si>
-    <t>Review DFS Solution</t>
-  </si>
-  <si>
-    <t>Connected Components</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 547 Number of Provinces </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/number-of-provinces/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Connected Components Pattern</t>
-  </si>
-  <si>
-    <t>Connected Components Pattern</t>
-  </si>
-  <si>
-    <t>DFS/BFS Applications, Island-Type Problems</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 200 Number of Islands </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/number-of-islands/</t>
-    </r>
-  </si>
-  <si>
-    <t>Read LC 994</t>
-  </si>
-  <si>
-    <t>Multi-Source BFS</t>
-  </si>
-  <si>
-    <t>BFS from Multiple Sources, Queue Expansion Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 994 Rotten Oranges </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/rotting-oranges/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Multi-Source BFS</t>
-  </si>
-  <si>
-    <t>Topological Sort Introduction</t>
-  </si>
-  <si>
-    <t>Dependency Graphs, DAG, Course Scheduling Concept</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 207 Course Schedule </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/course-schedule/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Topological Sort Notes</t>
-  </si>
-  <si>
-    <t>Island Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 695 Max Area of Island </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/max-area-of-island/</t>
-    </r>
-  </si>
-  <si>
-    <t>Multi-Source BFS Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 542 01 Matrix </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/01-matrix/</t>
-    </r>
-  </si>
-  <si>
-    <t>Topological Sort Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 210 Course Schedule II </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/course-schedule-ii/</t>
-    </r>
-  </si>
-  <si>
-    <t>Heap Fundamentals</t>
-  </si>
-  <si>
-    <t>Complete Binary Tree, Min Heap, Max Heap, Heap Property, Heap Representation</t>
-  </si>
-  <si>
-    <t>Visualize Heap using Excalidraw</t>
-  </si>
-  <si>
-    <t>Review Heap Terminology</t>
-  </si>
-  <si>
-    <t>Heap Operations</t>
-  </si>
-  <si>
-    <t>Insert, Delete, Heapify, Complexity Analysis, Priority Queue</t>
-  </si>
-  <si>
-    <t>Implement Min Heap using Python heapq</t>
-  </si>
-  <si>
-    <t>Read LC 215</t>
-  </si>
-  <si>
-    <t>Top-K Pattern</t>
-  </si>
-  <si>
-    <t>Why Heap is Better than Sorting, K Largest / K Smallest Problems, Priority Queue Thinking</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 215 Kth Largest Element in an Array </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/kth-largest-element-in-an-array/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Top-K Pattern Notes</t>
-  </si>
-  <si>
-    <t>Heap Basics</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 703 Kth Largest Element in a Stream </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/kth-largest-element-in-a-stream/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 1046 Last Stone Weight </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/last-stone-weight/</t>
-    </r>
-  </si>
-  <si>
-    <t>Priority Queue Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 973 K Closest Points to Origin </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/k-closest-points-to-origin/</t>
-    </r>
-  </si>
-  <si>
-    <t>Binary Search Fundamentals</t>
-  </si>
-  <si>
-    <t>Linear Search vs Binary Search, Prerequisites, Sorted Array Concept, Search Space Reduction</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 704 Binary Search </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/binary-search/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Binary Search Notes</t>
-  </si>
-  <si>
-    <t>Binary Search Implementation</t>
-  </si>
-  <si>
-    <t>Iterative Binary Search, Recursive Binary Search, Mid Calculation, Complexity Analysis</t>
-  </si>
-  <si>
-    <t>Implement Binary Search from Scratch</t>
-  </si>
-  <si>
-    <t>Read LC 35</t>
-  </si>
-  <si>
-    <t>Binary Search on Answer</t>
-  </si>
-  <si>
-    <t>Monotonic Functions, Search Space Thinking, Optimization Problems</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 875 Koko Eating Bananas </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/koko-eating-bananas/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Binary Search on Answer Notes</t>
-  </si>
-  <si>
-    <t>Basic Binary Search Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 35 Search Insert Position </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/search-insert-position/</t>
-    </r>
-  </si>
-  <si>
-    <t>Boundary Search Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 34 Find First and Last Position of Element in Sorted Array </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/find-first-and-last-position-of-element-in-sorted-array/</t>
-    </r>
-  </si>
-  <si>
-    <t>Binary Search on Answer Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 1011 Capacity To Ship Packages Within D Days </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/capacity-to-ship-packages-within-d-days/</t>
-    </r>
-  </si>
-  <si>
-    <t>Greedy Fundamentals</t>
-  </si>
-  <si>
-    <t>What is Greedy, Local Optimum vs Global Optimum, Greedy Choice Property, When Greedy Works</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 455 Assign Cookies </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/assign-cookies/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Greedy Notes</t>
-  </si>
-  <si>
-    <t>Greedy Strategy</t>
-  </si>
-  <si>
-    <t>Sorting + Greedy, Interval Thinking, Decision Making</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 605 Can Place Flowers </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/can-place-flowers/</t>
-    </r>
-  </si>
-  <si>
-    <t>Read LC 860</t>
-  </si>
-  <si>
-    <t>How to Identify Greedy Problems, Greedy vs DP, Common Greedy Patterns</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 860 Lemonade Change </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/lemonade-change/</t>
-    </r>
-  </si>
-  <si>
-    <t>Resource Allocation Pattern</t>
-  </si>
-  <si>
-    <t>Simulation + Greedy Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 55 Jump Game </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/jump-game/</t>
-    </r>
-  </si>
-  <si>
-    <t>Reachability &amp; Interval Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 452 Minimum Number of Arrows to Burst Balloons </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/minimum-number-of-arrows-to-burst-balloons/</t>
-    </r>
-  </si>
-  <si>
-    <t>Why DP Exists</t>
-  </si>
-  <si>
-    <t>Recursion Review, Overlapping Subproblems, Optimal Substructure</t>
-  </si>
-  <si>
-    <t>Memoization</t>
-  </si>
-  <si>
-    <t>Top-Down DP, Cache Concept, Avoiding Repeated Computation</t>
-  </si>
-  <si>
-    <t>LC 509 Fibonacci Memoization</t>
-  </si>
-  <si>
-    <t>Tabulation</t>
-  </si>
-  <si>
-    <t>Bottom-Up DP, State Transition, DP Array</t>
-  </si>
-  <si>
-    <t>Review DP Notes</t>
-  </si>
-  <si>
-    <t>Fibonacci Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 1137 N-th Tribonacci Number </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/n-th-tribonacci-number/</t>
-    </r>
-  </si>
-  <si>
-    <t>Climbing Stairs Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 746 Min Cost Climbing Stairs </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/min-cost-climbing-stairs/</t>
-    </r>
-  </si>
-  <si>
-    <t>DP State Recognition</t>
-  </si>
-  <si>
-    <t>DP Revision Worksheet</t>
-  </si>
-  <si>
-    <t>House Robber Pattern</t>
-  </si>
-  <si>
-    <t>State Definition, Decision Making, Include/Exclude</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 198 House Robber </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/house-robber/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review House Robber Pattern</t>
-  </si>
-  <si>
-    <t>DP Optimization</t>
-  </si>
-  <si>
-    <t>Space Optimization, Rolling Variables</t>
-  </si>
-  <si>
-    <t>LC 198 Walkthrough</t>
-  </si>
-  <si>
-    <t>Read LC 213</t>
-  </si>
-  <si>
-    <t>Coin Change Pattern</t>
-  </si>
-  <si>
-    <t>Minimum Coins, State Transition</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 322 Coin Change </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/coin-change/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Coin Change Notes</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 213 House Robber II </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/house-robber-ii/</t>
-    </r>
-  </si>
-  <si>
-    <t>Circular DP Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 740 Delete and Earn </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/delete-and-earn/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 518 Coin Change II </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/coin-change-ii/</t>
-    </r>
-  </si>
-  <si>
-    <t>Grid DP</t>
-  </si>
-  <si>
-    <t>Rows, Columns, State Transition Matrix</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 62 Unique Paths </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/unique-paths/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Grid DP Notes</t>
-  </si>
-  <si>
-    <t>Path-Based Optimization Problems</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 64 Minimum Path Sum </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/minimum-path-sum/</t>
-    </r>
-  </si>
-  <si>
-    <t>Read LC 63</t>
-  </si>
-  <si>
-    <t>Obstacle-Based DP</t>
-  </si>
-  <si>
-    <t>Handling Constraints in DP Grids</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 63 Unique Paths II </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/unique-paths-ii/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review State Transition</t>
-  </si>
-  <si>
-    <t>Unique Paths Pattern</t>
-  </si>
-  <si>
-    <t>Minimum Cost Path Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 931 Minimum Falling Path Sum </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/minimum-falling-path-sum/</t>
-    </r>
-  </si>
-  <si>
-    <t>Grid DP Pattern Recognition</t>
-  </si>
-  <si>
-    <t>Mixed Grid DP Discussion</t>
-  </si>
-  <si>
-    <t>Grid DP Revision</t>
-  </si>
-  <si>
-    <t>Longest Common Subsequence</t>
-  </si>
-  <si>
-    <t>Matching Decisions, 2D DP Table</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 1143 Longest Common Subsequence </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/longest-common-subsequence/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review LCS Notes</t>
-  </si>
-  <si>
-    <t>Edit Distance</t>
-  </si>
-  <si>
-    <t>Insert, Delete, Replace Operations</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 72 Edit Distance </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/edit-distance/</t>
-    </r>
-  </si>
-  <si>
-    <t>Review Edit Distance</t>
-  </si>
-  <si>
-    <t>Subset DP</t>
-  </si>
-  <si>
-    <t>Target Sum, Partition Problems, Pick/Not Pick Revisited</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 416 Partition Equal Subset Sum </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/partition-equal-subset-sum/</t>
-    </r>
-  </si>
-  <si>
-    <t>Read LC 494</t>
-  </si>
-  <si>
-    <t>LCS Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 583 Delete Operation for Two Strings </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>https://leetcode.com/problems/delete-operation-for-two-strings/</t>
-    </r>
-  </si>
-  <si>
-    <t>Partition Pattern</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">LC 494 Target Sum </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="19"/>
-        <rFont val="Calibri"/>
-      </rPr>
       <t>https://leetcode.com/problems/target-sum/</t>
     </r>
   </si>
@@ -3298,7 +3232,7 @@
     <t>Mixed DP Pattern Recognition</t>
   </si>
   <si>
-    <t>DP Pattern Identification Workshop</t>
+    <t>LC 300 Longest Increasing Subsequence</t>
   </si>
   <si>
     <t>DP Consolidation Sheet</t>
@@ -9360,7 +9294,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="38" ht="39.1" customHeight="1">
+    <row r="38" ht="26.1" customHeight="1">
       <c r="A38" s="24">
         <v>36</v>
       </c>
@@ -9460,7 +9394,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="43" ht="26.1" customHeight="1">
+    <row r="43" ht="19.1" customHeight="1">
       <c r="A43" s="24">
         <v>41</v>
       </c>
@@ -9474,10 +9408,10 @@
         <v>161</v>
       </c>
       <c r="E43" t="s" s="28">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F43" t="s" s="28">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" ht="26.1" customHeight="1">
@@ -9497,7 +9431,7 @@
         <v>157</v>
       </c>
       <c r="F44" t="s" s="28">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" ht="26.1" customHeight="1">
@@ -9508,13 +9442,13 @@
         <v>4</v>
       </c>
       <c r="C45" t="s" s="26">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D45" t="s" s="27">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E45" t="s" s="28">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F45" t="s" s="27">
         <v>153</v>
@@ -9528,16 +9462,16 @@
         <v>4</v>
       </c>
       <c r="C46" t="s" s="26">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D46" t="s" s="27">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E46" t="s" s="27">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F46" t="s" s="28">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" ht="13.1" customHeight="1">
@@ -9548,13 +9482,13 @@
         <v>4</v>
       </c>
       <c r="C47" t="s" s="26">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D47" t="s" s="27">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E47" t="s" s="27">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F47" t="s" s="27">
         <v>149</v>
@@ -9571,13 +9505,13 @@
         <v>37</v>
       </c>
       <c r="D48" t="s" s="27">
+        <v>168</v>
+      </c>
+      <c r="E48" t="s" s="28">
         <v>167</v>
       </c>
-      <c r="E48" t="s" s="28">
-        <v>166</v>
-      </c>
       <c r="F48" t="s" s="28">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" ht="26.1" customHeight="1">
@@ -9591,13 +9525,13 @@
         <v>37</v>
       </c>
       <c r="D49" t="s" s="27">
+        <v>172</v>
+      </c>
+      <c r="E49" t="s" s="28">
         <v>171</v>
       </c>
-      <c r="E49" t="s" s="28">
-        <v>170</v>
-      </c>
       <c r="F49" t="s" s="28">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" ht="39.1" customHeight="1">
@@ -9611,13 +9545,13 @@
         <v>37</v>
       </c>
       <c r="D50" t="s" s="27">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E50" t="s" s="28">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F50" t="s" s="28">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" ht="26.1" customHeight="1">
@@ -9628,13 +9562,13 @@
         <v>4</v>
       </c>
       <c r="C51" t="s" s="26">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D51" t="s" s="27">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E51" t="s" s="28">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F51" t="s" s="27">
         <v>153</v>
@@ -9648,13 +9582,13 @@
         <v>4</v>
       </c>
       <c r="C52" t="s" s="26">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D52" t="s" s="27">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E52" t="s" s="28">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F52" t="s" s="27">
         <v>149</v>
@@ -9668,16 +9602,16 @@
         <v>4</v>
       </c>
       <c r="C53" t="s" s="26">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D53" t="s" s="27">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E53" t="s" s="27">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F53" t="s" s="27">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" ht="26.1" customHeight="1">
@@ -9691,13 +9625,13 @@
         <v>37</v>
       </c>
       <c r="D54" t="s" s="27">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E54" t="s" s="28">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F54" t="s" s="28">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" ht="26.1" customHeight="1">
@@ -9711,13 +9645,13 @@
         <v>37</v>
       </c>
       <c r="D55" t="s" s="27">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E55" t="s" s="28">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F55" t="s" s="28">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" ht="26.1" customHeight="1">
@@ -9731,13 +9665,13 @@
         <v>37</v>
       </c>
       <c r="D56" t="s" s="27">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E56" t="s" s="28">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F56" t="s" s="28">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" ht="26.1" customHeight="1">
@@ -9748,16 +9682,16 @@
         <v>16</v>
       </c>
       <c r="C57" t="s" s="26">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D57" t="s" s="27">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E57" t="s" s="28">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F57" t="s" s="27">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" ht="26.1" customHeight="1">
@@ -9768,16 +9702,16 @@
         <v>16</v>
       </c>
       <c r="C58" t="s" s="26">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D58" t="s" s="27">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E58" t="s" s="28">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="F58" t="s" s="27">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" ht="26.1" customHeight="1">
@@ -9788,16 +9722,16 @@
         <v>16</v>
       </c>
       <c r="C59" t="s" s="26">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D59" t="s" s="27">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E59" t="s" s="28">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F59" t="s" s="27">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" ht="26.1" customHeight="1">
@@ -9811,13 +9745,13 @@
         <v>37</v>
       </c>
       <c r="D60" t="s" s="27">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E60" t="s" s="28">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F60" t="s" s="28">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61" ht="26.1" customHeight="1">
@@ -9831,13 +9765,13 @@
         <v>37</v>
       </c>
       <c r="D61" t="s" s="27">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E61" t="s" s="28">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="F61" t="s" s="28">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" ht="26.1" customHeight="1">
@@ -9851,13 +9785,13 @@
         <v>37</v>
       </c>
       <c r="D62" t="s" s="27">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E62" t="s" s="28">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F62" t="s" s="28">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" ht="13.1" customHeight="1">
@@ -9868,19 +9802,19 @@
         <v>16</v>
       </c>
       <c r="C63" t="s" s="26">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D63" t="s" s="27">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E63" t="s" s="28">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F63" t="s" s="27">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="64" ht="26.1" customHeight="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="64" ht="13.1" customHeight="1">
       <c r="A64" s="24">
         <v>62</v>
       </c>
@@ -9888,16 +9822,16 @@
         <v>16</v>
       </c>
       <c r="C64" t="s" s="26">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D64" t="s" s="27">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E64" t="s" s="28">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F64" t="s" s="27">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="65" ht="26.1" customHeight="1">
@@ -9908,16 +9842,16 @@
         <v>16</v>
       </c>
       <c r="C65" t="s" s="26">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D65" t="s" s="27">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E65" t="s" s="28">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F65" t="s" s="27">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" ht="19.1" customHeight="1">
@@ -9931,13 +9865,13 @@
         <v>37</v>
       </c>
       <c r="D66" t="s" s="27">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E66" t="s" s="28">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F66" t="s" s="28">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67" ht="26.1" customHeight="1">
@@ -9951,13 +9885,13 @@
         <v>37</v>
       </c>
       <c r="D67" t="s" s="27">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E67" t="s" s="28">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="F67" t="s" s="28">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="68" ht="26.1" customHeight="1">
@@ -9971,13 +9905,13 @@
         <v>37</v>
       </c>
       <c r="D68" t="s" s="27">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E68" t="s" s="28">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F68" t="s" s="28">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="69" ht="26.1" customHeight="1">
@@ -9988,16 +9922,16 @@
         <v>10</v>
       </c>
       <c r="C69" t="s" s="26">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D69" t="s" s="27">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E69" t="s" s="27">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F69" t="s" s="27">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="70" ht="13.1" customHeight="1">
@@ -10008,16 +9942,16 @@
         <v>10</v>
       </c>
       <c r="C70" t="s" s="26">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D70" t="s" s="27">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E70" t="s" s="27">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F70" t="s" s="27">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="71" ht="26.1" customHeight="1">
@@ -10028,16 +9962,16 @@
         <v>10</v>
       </c>
       <c r="C71" t="s" s="26">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D71" t="s" s="27">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E71" t="s" s="28">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F71" t="s" s="27">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72" ht="26.1" customHeight="1">
@@ -10051,13 +9985,13 @@
         <v>37</v>
       </c>
       <c r="D72" t="s" s="27">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E72" t="s" s="28">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F72" t="s" s="28">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" ht="26.1" customHeight="1">
@@ -10071,13 +10005,13 @@
         <v>37</v>
       </c>
       <c r="D73" t="s" s="27">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E73" t="s" s="28">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F73" t="s" s="28">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" ht="26.1" customHeight="1">
@@ -10091,13 +10025,13 @@
         <v>37</v>
       </c>
       <c r="D74" t="s" s="27">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E74" t="s" s="28">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F74" t="s" s="28">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75" ht="26.1" customHeight="1">
@@ -10108,16 +10042,16 @@
         <v>15</v>
       </c>
       <c r="C75" t="s" s="26">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D75" t="s" s="27">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E75" t="s" s="27">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F75" t="s" s="27">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="76" ht="13.1" customHeight="1">
@@ -10128,16 +10062,16 @@
         <v>15</v>
       </c>
       <c r="C76" t="s" s="26">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D76" t="s" s="27">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E76" t="s" s="27">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F76" t="s" s="27">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="77" ht="26.1" customHeight="1">
@@ -10148,16 +10082,16 @@
         <v>15</v>
       </c>
       <c r="C77" t="s" s="26">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D77" t="s" s="27">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E77" t="s" s="28">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F77" t="s" s="27">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="78" ht="26.1" customHeight="1">
@@ -10171,13 +10105,13 @@
         <v>37</v>
       </c>
       <c r="D78" t="s" s="27">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E78" t="s" s="28">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F78" t="s" s="28">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="79" ht="26.1" customHeight="1">
@@ -10191,13 +10125,13 @@
         <v>37</v>
       </c>
       <c r="D79" t="s" s="27">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E79" t="s" s="28">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F79" t="s" s="28">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="80" ht="26.1" customHeight="1">
@@ -10211,13 +10145,13 @@
         <v>37</v>
       </c>
       <c r="D80" t="s" s="27">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E80" t="s" s="28">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F80" t="s" s="28">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="81" ht="26.1" customHeight="1">
@@ -10228,16 +10162,16 @@
         <v>12</v>
       </c>
       <c r="C81" t="s" s="26">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D81" t="s" s="27">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E81" t="s" s="27">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F81" t="s" s="27">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="82" ht="26.1" customHeight="1">
@@ -10248,16 +10182,16 @@
         <v>12</v>
       </c>
       <c r="C82" t="s" s="26">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D82" t="s" s="27">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E82" t="s" s="27">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F82" t="s" s="27">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="83" ht="26.1" customHeight="1">
@@ -10268,16 +10202,16 @@
         <v>12</v>
       </c>
       <c r="C83" t="s" s="26">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D83" t="s" s="27">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E83" t="s" s="28">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F83" t="s" s="27">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="84" ht="26.1" customHeight="1">
@@ -10291,13 +10225,13 @@
         <v>37</v>
       </c>
       <c r="D84" t="s" s="27">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E84" t="s" s="28">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F84" t="s" s="28">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="85" ht="26.1" customHeight="1">
@@ -10311,13 +10245,13 @@
         <v>37</v>
       </c>
       <c r="D85" t="s" s="27">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E85" t="s" s="28">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F85" t="s" s="27">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="86" ht="26.1" customHeight="1">
@@ -10331,13 +10265,13 @@
         <v>37</v>
       </c>
       <c r="D86" t="s" s="27">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E86" t="s" s="28">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F86" t="s" s="27">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="87" ht="26.1" customHeight="1">
@@ -10348,16 +10282,16 @@
         <v>13</v>
       </c>
       <c r="C87" t="s" s="26">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D87" t="s" s="27">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E87" t="s" s="27">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F87" t="s" s="27">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="88" ht="26.1" customHeight="1">
@@ -10368,19 +10302,19 @@
         <v>13</v>
       </c>
       <c r="C88" t="s" s="26">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D88" t="s" s="27">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E88" t="s" s="28">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F88" t="s" s="27">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="89" ht="26.1" customHeight="1">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="89" ht="13.1" customHeight="1">
       <c r="A89" s="24">
         <v>87</v>
       </c>
@@ -10388,16 +10322,16 @@
         <v>13</v>
       </c>
       <c r="C89" t="s" s="26">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D89" t="s" s="27">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E89" t="s" s="28">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F89" t="s" s="27">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="90" ht="26.1" customHeight="1">
@@ -10411,13 +10345,13 @@
         <v>37</v>
       </c>
       <c r="D90" t="s" s="27">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E90" t="s" s="28">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F90" t="s" s="28">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="91" ht="26.1" customHeight="1">
@@ -10431,13 +10365,13 @@
         <v>37</v>
       </c>
       <c r="D91" t="s" s="27">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E91" t="s" s="28">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F91" t="s" s="28">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="92" ht="26.1" customHeight="1">
@@ -10451,13 +10385,13 @@
         <v>37</v>
       </c>
       <c r="D92" t="s" s="27">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E92" t="s" s="28">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="F92" t="s" s="27">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="93" ht="13.1" customHeight="1">
@@ -10468,16 +10402,16 @@
         <v>13</v>
       </c>
       <c r="C93" t="s" s="26">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D93" t="s" s="27">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E93" t="s" s="27">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F93" t="s" s="27">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="94" ht="13.1" customHeight="1">
@@ -10488,16 +10422,16 @@
         <v>13</v>
       </c>
       <c r="C94" t="s" s="26">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D94" t="s" s="27">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E94" t="s" s="28">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F94" t="s" s="27">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="95" ht="26.1" customHeight="1">
@@ -10508,16 +10442,16 @@
         <v>13</v>
       </c>
       <c r="C95" t="s" s="26">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D95" t="s" s="27">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E95" t="s" s="28">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F95" t="s" s="27">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="96" ht="19.1" customHeight="1">
@@ -10531,13 +10465,13 @@
         <v>37</v>
       </c>
       <c r="D96" t="s" s="27">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E96" t="s" s="28">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F96" t="s" s="28">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="97" ht="26.1" customHeight="1">
@@ -10551,13 +10485,13 @@
         <v>37</v>
       </c>
       <c r="D97" t="s" s="27">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E97" t="s" s="28">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F97" t="s" s="28">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="98" ht="26.1" customHeight="1">
@@ -10571,13 +10505,13 @@
         <v>37</v>
       </c>
       <c r="D98" t="s" s="27">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E98" t="s" s="28">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F98" t="s" s="28">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="99" ht="26.1" customHeight="1">
@@ -10588,16 +10522,16 @@
         <v>17</v>
       </c>
       <c r="C99" t="s" s="26">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D99" t="s" s="27">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E99" t="s" s="27">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F99" t="s" s="27">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="100" ht="26.1" customHeight="1">
@@ -10608,16 +10542,16 @@
         <v>17</v>
       </c>
       <c r="C100" t="s" s="26">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D100" t="s" s="27">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E100" t="s" s="28">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F100" t="s" s="27">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="101" ht="26.1" customHeight="1">
@@ -10628,16 +10562,16 @@
         <v>17</v>
       </c>
       <c r="C101" t="s" s="26">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D101" t="s" s="27">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E101" t="s" s="28">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F101" t="s" s="27">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="102" ht="26.1" customHeight="1">
@@ -10651,13 +10585,13 @@
         <v>37</v>
       </c>
       <c r="D102" t="s" s="27">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E102" t="s" s="28">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F102" t="s" s="28">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="103" ht="26.1" customHeight="1">
@@ -10671,13 +10605,13 @@
         <v>37</v>
       </c>
       <c r="D103" t="s" s="27">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E103" t="s" s="28">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F103" t="s" s="28">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="104" ht="26.1" customHeight="1">
@@ -10691,13 +10625,13 @@
         <v>37</v>
       </c>
       <c r="D104" t="s" s="27">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E104" t="s" s="28">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F104" t="s" s="28">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="105" ht="26.1" customHeight="1">
@@ -10708,16 +10642,16 @@
         <v>17</v>
       </c>
       <c r="C105" t="s" s="26">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D105" t="s" s="27">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E105" t="s" s="28">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F105" t="s" s="27">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="106" ht="26.1" customHeight="1">
@@ -10728,16 +10662,16 @@
         <v>17</v>
       </c>
       <c r="C106" t="s" s="26">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D106" t="s" s="27">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E106" t="s" s="28">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F106" t="s" s="27">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="107" ht="26.1" customHeight="1">
@@ -10748,16 +10682,16 @@
         <v>17</v>
       </c>
       <c r="C107" t="s" s="26">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D107" t="s" s="27">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E107" t="s" s="28">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F107" t="s" s="27">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="108" ht="26.1" customHeight="1">
@@ -10771,13 +10705,13 @@
         <v>37</v>
       </c>
       <c r="D108" t="s" s="27">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E108" t="s" s="28">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F108" t="s" s="28">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="109" ht="26.1" customHeight="1">
@@ -10791,13 +10725,13 @@
         <v>37</v>
       </c>
       <c r="D109" t="s" s="27">
+        <v>353</v>
+      </c>
+      <c r="E109" t="s" s="28">
+        <v>345</v>
+      </c>
+      <c r="F109" t="s" s="28">
         <v>349</v>
-      </c>
-      <c r="E109" t="s" s="28">
-        <v>341</v>
-      </c>
-      <c r="F109" t="s" s="28">
-        <v>345</v>
       </c>
     </row>
     <row r="110" ht="26.1" customHeight="1">
@@ -10811,13 +10745,13 @@
         <v>37</v>
       </c>
       <c r="D110" t="s" s="27">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E110" t="s" s="28">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F110" t="s" s="28">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="111" ht="26.1" customHeight="1">
@@ -10828,16 +10762,16 @@
         <v>7</v>
       </c>
       <c r="C111" t="s" s="26">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D111" t="s" s="27">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E111" t="s" s="27">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="F111" t="s" s="27">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="112" ht="13.1" customHeight="1">
@@ -10848,16 +10782,16 @@
         <v>7</v>
       </c>
       <c r="C112" t="s" s="26">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D112" t="s" s="27">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E112" t="s" s="27">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F112" t="s" s="27">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" ht="26.1" customHeight="1">
@@ -10868,16 +10802,16 @@
         <v>7</v>
       </c>
       <c r="C113" t="s" s="26">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D113" t="s" s="27">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E113" t="s" s="28">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F113" t="s" s="27">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="114" ht="26.1" customHeight="1">
@@ -10891,13 +10825,13 @@
         <v>37</v>
       </c>
       <c r="D114" t="s" s="27">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E114" t="s" s="28">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F114" t="s" s="28">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="115" ht="26.1" customHeight="1">
@@ -10911,13 +10845,13 @@
         <v>37</v>
       </c>
       <c r="D115" t="s" s="27">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E115" t="s" s="28">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F115" t="s" s="27">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="116" ht="26.1" customHeight="1">
@@ -10931,13 +10865,13 @@
         <v>37</v>
       </c>
       <c r="D116" t="s" s="27">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E116" t="s" s="28">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F116" t="s" s="27">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="117" ht="26.1" customHeight="1">
@@ -10948,16 +10882,16 @@
         <v>7</v>
       </c>
       <c r="C117" t="s" s="26">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D117" t="s" s="27">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E117" t="s" s="28">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F117" t="s" s="27">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="118" ht="26.1" customHeight="1">
@@ -10968,16 +10902,16 @@
         <v>7</v>
       </c>
       <c r="C118" t="s" s="26">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D118" t="s" s="27">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E118" t="s" s="28">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F118" t="s" s="27">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" ht="26.1" customHeight="1">
@@ -10988,16 +10922,16 @@
         <v>7</v>
       </c>
       <c r="C119" t="s" s="26">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D119" t="s" s="27">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E119" t="s" s="28">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F119" t="s" s="27">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="120" ht="26.1" customHeight="1">
@@ -11011,13 +10945,13 @@
         <v>37</v>
       </c>
       <c r="D120" t="s" s="27">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E120" t="s" s="28">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F120" t="s" s="28">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="121" ht="26.1" customHeight="1">
@@ -11031,13 +10965,13 @@
         <v>37</v>
       </c>
       <c r="D121" t="s" s="27">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E121" t="s" s="28">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F121" t="s" s="28">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" ht="26.1" customHeight="1">
@@ -11051,13 +10985,13 @@
         <v>37</v>
       </c>
       <c r="D122" t="s" s="27">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E122" t="s" s="28">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F122" t="s" s="28">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="123" ht="26.1" customHeight="1">
@@ -11068,16 +11002,16 @@
         <v>9</v>
       </c>
       <c r="C123" t="s" s="26">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D123" t="s" s="27">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E123" t="s" s="27">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F123" t="s" s="27">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="124" ht="13.1" customHeight="1">
@@ -11088,16 +11022,16 @@
         <v>9</v>
       </c>
       <c r="C124" t="s" s="26">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D124" t="s" s="27">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E124" t="s" s="27">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F124" t="s" s="27">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="125" ht="26.1" customHeight="1">
@@ -11108,16 +11042,16 @@
         <v>9</v>
       </c>
       <c r="C125" t="s" s="26">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D125" t="s" s="27">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E125" t="s" s="28">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F125" t="s" s="27">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="126" ht="26.1" customHeight="1">
@@ -11131,13 +11065,13 @@
         <v>37</v>
       </c>
       <c r="D126" t="s" s="27">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E126" t="s" s="28">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F126" t="s" s="28">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="127" ht="26.1" customHeight="1">
@@ -11151,13 +11085,13 @@
         <v>37</v>
       </c>
       <c r="D127" t="s" s="27">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E127" t="s" s="28">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F127" t="s" s="28">
-        <v>226</v>
+        <v>409</v>
       </c>
     </row>
     <row r="128" ht="26.1" customHeight="1">
@@ -11171,13 +11105,13 @@
         <v>37</v>
       </c>
       <c r="D128" t="s" s="27">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E128" t="s" s="28">
-        <v>226</v>
+        <v>409</v>
       </c>
       <c r="F128" t="s" s="28">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="129" ht="26.1" customHeight="1">
@@ -11188,16 +11122,16 @@
         <v>5</v>
       </c>
       <c r="C129" t="s" s="26">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D129" t="s" s="27">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E129" t="s" s="28">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F129" t="s" s="27">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="130" ht="26.1" customHeight="1">
@@ -11208,16 +11142,16 @@
         <v>5</v>
       </c>
       <c r="C130" t="s" s="26">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D130" t="s" s="27">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E130" t="s" s="27">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F130" t="s" s="27">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="131" ht="26.1" customHeight="1">
@@ -11228,16 +11162,16 @@
         <v>5</v>
       </c>
       <c r="C131" t="s" s="26">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="D131" t="s" s="27">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E131" t="s" s="28">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F131" t="s" s="27">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="132" ht="26.1" customHeight="1">
@@ -11251,13 +11185,13 @@
         <v>37</v>
       </c>
       <c r="D132" t="s" s="27">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E132" t="s" s="28">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F132" t="s" s="28">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="133" ht="39.1" customHeight="1">
@@ -11271,13 +11205,13 @@
         <v>37</v>
       </c>
       <c r="D133" t="s" s="27">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="E133" t="s" s="28">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="F133" t="s" s="28">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="134" ht="26.1" customHeight="1">
@@ -11291,13 +11225,13 @@
         <v>37</v>
       </c>
       <c r="D134" t="s" s="27">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E134" t="s" s="28">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F134" t="s" s="28">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="135" ht="26.1" customHeight="1">
@@ -11308,16 +11242,16 @@
         <v>8</v>
       </c>
       <c r="C135" t="s" s="26">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D135" t="s" s="27">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="E135" t="s" s="28">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="F135" t="s" s="27">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="136" ht="26.1" customHeight="1">
@@ -11328,16 +11262,16 @@
         <v>8</v>
       </c>
       <c r="C136" t="s" s="26">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D136" t="s" s="27">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="E136" t="s" s="28">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F136" t="s" s="27">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="137" ht="26.1" customHeight="1">
@@ -11348,16 +11282,16 @@
         <v>8</v>
       </c>
       <c r="C137" t="s" s="26">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D137" t="s" s="27">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E137" t="s" s="28">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F137" t="s" s="27">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="138" ht="26.1" customHeight="1">
@@ -11371,13 +11305,13 @@
         <v>37</v>
       </c>
       <c r="D138" t="s" s="27">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="E138" t="s" s="28">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="F138" t="s" s="28">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="139" ht="26.1" customHeight="1">
@@ -11391,13 +11325,13 @@
         <v>37</v>
       </c>
       <c r="D139" t="s" s="27">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E139" t="s" s="28">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F139" t="s" s="28">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="140" ht="26.1" customHeight="1">
@@ -11411,16 +11345,16 @@
         <v>37</v>
       </c>
       <c r="D140" t="s" s="27">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="E140" t="s" s="28">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F140" t="s" s="28">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="141" ht="26.1" customHeight="1">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="141" ht="13.1" customHeight="1">
       <c r="A141" s="24">
         <v>139</v>
       </c>
@@ -11428,16 +11362,16 @@
         <v>6</v>
       </c>
       <c r="C141" t="s" s="26">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D141" t="s" s="27">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="E141" t="s" s="28">
-        <v>291</v>
+        <v>447</v>
       </c>
       <c r="F141" t="s" s="27">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="142" ht="13.1" customHeight="1">
@@ -11448,16 +11382,16 @@
         <v>6</v>
       </c>
       <c r="C142" t="s" s="26">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="D142" t="s" s="27">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E142" t="s" s="27">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="F142" t="s" s="27">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="143" ht="26.1" customHeight="1">
@@ -11468,16 +11402,16 @@
         <v>6</v>
       </c>
       <c r="C143" t="s" s="26">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D143" t="s" s="27">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="E143" t="s" s="28">
-        <v>295</v>
+        <v>453</v>
       </c>
       <c r="F143" t="s" s="27">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="144" ht="26.1" customHeight="1">
@@ -11491,13 +11425,13 @@
         <v>37</v>
       </c>
       <c r="D144" t="s" s="27">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="E144" t="s" s="28">
-        <v>291</v>
+        <v>456</v>
       </c>
       <c r="F144" t="s" s="28">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="145" ht="26.1" customHeight="1">
@@ -11511,13 +11445,13 @@
         <v>37</v>
       </c>
       <c r="D145" t="s" s="27">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="E145" t="s" s="28">
-        <v>295</v>
+        <v>453</v>
       </c>
       <c r="F145" t="s" s="28">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="146" ht="26.1" customHeight="1">
@@ -11531,13 +11465,13 @@
         <v>37</v>
       </c>
       <c r="D146" t="s" s="27">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="E146" t="s" s="28">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F146" t="s" s="27">
-        <v>453</v>
+        <v>461</v>
       </c>
     </row>
     <row r="147" ht="26.1" customHeight="1">
@@ -11548,16 +11482,16 @@
         <v>6</v>
       </c>
       <c r="C147" t="s" s="26">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="D147" t="s" s="27">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E147" t="s" s="28">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="F147" t="s" s="27">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="148" ht="13.1" customHeight="1">
@@ -11568,16 +11502,16 @@
         <v>6</v>
       </c>
       <c r="C148" t="s" s="26">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="D148" t="s" s="27">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E148" t="s" s="27">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="F148" t="s" s="27">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="149" ht="13.1" customHeight="1">
@@ -11588,16 +11522,16 @@
         <v>6</v>
       </c>
       <c r="C149" t="s" s="26">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="D149" t="s" s="27">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="E149" t="s" s="28">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="F149" t="s" s="27">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="150" ht="26.1" customHeight="1">
@@ -11611,13 +11545,13 @@
         <v>37</v>
       </c>
       <c r="D150" t="s" s="27">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="E150" t="s" s="28">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="F150" t="s" s="28">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="151" ht="26.1" customHeight="1">
@@ -11631,13 +11565,13 @@
         <v>37</v>
       </c>
       <c r="D151" t="s" s="27">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E151" t="s" s="28">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="F151" t="s" s="28">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="152" ht="19.1" customHeight="1">
@@ -11651,13 +11585,13 @@
         <v>37</v>
       </c>
       <c r="D152" t="s" s="27">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E152" t="s" s="28">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="F152" t="s" s="28">
-        <v>469</v>
+        <v>477</v>
       </c>
     </row>
     <row r="153" ht="13.1" customHeight="1">
@@ -11668,16 +11602,16 @@
         <v>6</v>
       </c>
       <c r="C153" t="s" s="26">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="D153" t="s" s="27">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="E153" t="s" s="28">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="F153" t="s" s="27">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="154" ht="26.1" customHeight="1">
@@ -11688,16 +11622,16 @@
         <v>6</v>
       </c>
       <c r="C154" t="s" s="26">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="D154" t="s" s="27">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="E154" t="s" s="28">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="F154" t="s" s="27">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="155" ht="26.1" customHeight="1">
@@ -11708,16 +11642,16 @@
         <v>6</v>
       </c>
       <c r="C155" t="s" s="26">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D155" t="s" s="27">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E155" t="s" s="28">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="F155" t="s" s="27">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="156" ht="19.1" customHeight="1">
@@ -11731,13 +11665,13 @@
         <v>37</v>
       </c>
       <c r="D156" t="s" s="27">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E156" t="s" s="28">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="F156" t="s" s="28">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="157" ht="26.1" customHeight="1">
@@ -11751,13 +11685,13 @@
         <v>37</v>
       </c>
       <c r="D157" t="s" s="27">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E157" t="s" s="28">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="F157" t="s" s="28">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="158" ht="19.1" customHeight="1">
@@ -11771,13 +11705,13 @@
         <v>37</v>
       </c>
       <c r="D158" t="s" s="27">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="E158" t="s" s="27">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="F158" t="s" s="27">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="159" ht="26.1" customHeight="1">
@@ -11788,16 +11722,16 @@
         <v>6</v>
       </c>
       <c r="C159" t="s" s="26">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="D159" t="s" s="27">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="E159" t="s" s="28">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="F159" t="s" s="27">
-        <v>490</v>
+        <v>498</v>
       </c>
     </row>
     <row r="160" ht="13.1" customHeight="1">
@@ -11808,16 +11742,16 @@
         <v>6</v>
       </c>
       <c r="C160" t="s" s="26">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="D160" t="s" s="27">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="E160" t="s" s="28">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="F160" t="s" s="27">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="161" ht="26.1" customHeight="1">
@@ -11828,16 +11762,16 @@
         <v>6</v>
       </c>
       <c r="C161" t="s" s="26">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D161" t="s" s="27">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E161" t="s" s="28">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="F161" t="s" s="27">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="162" ht="26.1" customHeight="1">
@@ -11851,13 +11785,13 @@
         <v>37</v>
       </c>
       <c r="D162" t="s" s="27">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="E162" t="s" s="28">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="F162" t="s" s="28">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="163" ht="26.1" customHeight="1">
@@ -11871,13 +11805,13 @@
         <v>37</v>
       </c>
       <c r="D163" t="s" s="27">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="E163" t="s" s="28">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="F163" t="s" s="28">
-        <v>502</v>
+        <v>510</v>
       </c>
     </row>
     <row r="164" ht="19.1" customHeight="1">
@@ -11891,13 +11825,13 @@
         <v>37</v>
       </c>
       <c r="D164" t="s" s="27">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="E164" t="s" s="27">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="F164" t="s" s="27">
-        <v>505</v>
+        <v>513</v>
       </c>
     </row>
     <row r="165" ht="26.1" customHeight="1">
@@ -11908,16 +11842,16 @@
         <v>14</v>
       </c>
       <c r="C165" t="s" s="27">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="D165" t="s" s="27">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="E165" t="s" s="27">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="F165" t="s" s="28">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="166" ht="26.1" customHeight="1">
@@ -11928,16 +11862,16 @@
         <v>14</v>
       </c>
       <c r="C166" t="s" s="27">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="D166" t="s" s="27">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E166" t="s" s="27">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="F166" t="s" s="28">
-        <v>513</v>
+        <v>521</v>
       </c>
     </row>
     <row r="167" ht="26.1" customHeight="1">
@@ -11948,16 +11882,16 @@
         <v>14</v>
       </c>
       <c r="C167" t="s" s="27">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D167" t="s" s="27">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="E167" t="s" s="27">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="F167" t="s" s="27">
-        <v>517</v>
+        <v>525</v>
       </c>
     </row>
     <row r="168" ht="26.1" customHeight="1">
@@ -11968,16 +11902,16 @@
         <v>14</v>
       </c>
       <c r="C168" t="s" s="27">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D168" t="s" s="27">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="E168" t="s" s="28">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="F168" t="s" s="28">
-        <v>521</v>
+        <v>529</v>
       </c>
     </row>
     <row r="169" ht="26.1" customHeight="1">
@@ -11988,16 +11922,16 @@
         <v>14</v>
       </c>
       <c r="C169" t="s" s="27">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D169" t="s" s="27">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="E169" t="s" s="28">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="F169" t="s" s="28">
-        <v>523</v>
+        <v>531</v>
       </c>
     </row>
     <row r="170" ht="26.1" customHeight="1">
@@ -12008,16 +11942,16 @@
         <v>14</v>
       </c>
       <c r="C170" t="s" s="27">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D170" t="s" s="27">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="E170" t="s" s="28">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="F170" t="s" s="27">
-        <v>526</v>
+        <v>534</v>
       </c>
     </row>
     <row r="171" ht="26.1" customHeight="1">
@@ -12028,16 +11962,16 @@
         <v>14</v>
       </c>
       <c r="C171" t="s" s="27">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="D171" t="s" s="27">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="E171" t="s" s="27">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="F171" t="s" s="28">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="172" ht="13.1" customHeight="1">
@@ -12048,16 +11982,16 @@
         <v>14</v>
       </c>
       <c r="C172" t="s" s="27">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="D172" t="s" s="27">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="E172" t="s" s="27">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="F172" t="s" s="27">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="173" ht="26.1" customHeight="1">
@@ -12068,16 +12002,16 @@
         <v>14</v>
       </c>
       <c r="C173" t="s" s="27">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="D173" t="s" s="27">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="E173" t="s" s="27">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="F173" t="s" s="27">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="174" ht="39.1" customHeight="1">
@@ -12088,16 +12022,16 @@
         <v>14</v>
       </c>
       <c r="C174" t="s" s="27">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D174" t="s" s="27">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="E174" t="s" s="28">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="F174" t="s" s="28">
-        <v>541</v>
+        <v>549</v>
       </c>
     </row>
     <row r="175" ht="39.1" customHeight="1">
@@ -12108,16 +12042,16 @@
         <v>14</v>
       </c>
       <c r="C175" t="s" s="27">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D175" t="s" s="27">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="E175" t="s" s="28">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="F175" t="s" s="28">
-        <v>544</v>
+        <v>552</v>
       </c>
     </row>
     <row r="176" ht="26.1" customHeight="1">
@@ -12128,16 +12062,16 @@
         <v>14</v>
       </c>
       <c r="C176" t="s" s="27">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D176" t="s" s="27">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="E176" t="s" s="28">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="F176" t="s" s="27">
-        <v>547</v>
+        <v>555</v>
       </c>
     </row>
     <row r="177" ht="13.1" customHeight="1">
@@ -12148,16 +12082,16 @@
         <v>14</v>
       </c>
       <c r="C177" t="s" s="27">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="D177" t="s" s="27">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="E177" t="s" s="27">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="F177" t="s" s="27">
-        <v>551</v>
+        <v>559</v>
       </c>
     </row>
     <row r="178" ht="13.1" customHeight="1">
@@ -12168,16 +12102,16 @@
         <v>14</v>
       </c>
       <c r="C178" t="s" s="27">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D178" t="s" s="27">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="E178" t="s" s="27">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="F178" t="s" s="27">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="179" ht="26.1" customHeight="1">
@@ -12188,16 +12122,16 @@
         <v>14</v>
       </c>
       <c r="C179" t="s" s="27">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="D179" t="s" s="27">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="E179" t="s" s="27">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="F179" t="s" s="27">
-        <v>559</v>
+        <v>567</v>
       </c>
     </row>
     <row r="180" ht="26.1" customHeight="1">
@@ -12208,16 +12142,16 @@
         <v>14</v>
       </c>
       <c r="C180" t="s" s="27">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D180" t="s" s="27">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="E180" t="s" s="28">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="F180" t="s" s="28">
-        <v>562</v>
+        <v>570</v>
       </c>
     </row>
     <row r="181" ht="26.1" customHeight="1">
@@ -12228,16 +12162,16 @@
         <v>14</v>
       </c>
       <c r="C181" t="s" s="27">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D181" t="s" s="27">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="E181" t="s" s="28">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="F181" t="s" s="27">
-        <v>565</v>
+        <v>573</v>
       </c>
     </row>
     <row r="182" ht="26.1" customHeight="1">
@@ -12248,16 +12182,16 @@
         <v>14</v>
       </c>
       <c r="C182" t="s" s="27">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="D182" t="s" s="27">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="E182" t="s" s="27">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="F182" t="s" s="27">
-        <v>569</v>
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -12265,189 +12199,176 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E36" r:id="rId1" location="" tooltip="" display="https://leetcode.com/problems/two-sum/"/>
-    <hyperlink ref="F36" r:id="rId2" location="" tooltip="" display="https://leetcode.com/problems/contains-duplicate/"/>
-    <hyperlink ref="E37" r:id="rId3" location="" tooltip="" display="https://leetcode.com/problems/contains-duplicate/"/>
-    <hyperlink ref="F37" r:id="rId4" location="" tooltip="" display="https://leetcode.com/problems/valid-anagram/"/>
-    <hyperlink ref="E38" r:id="rId5" location="" tooltip="" display="https://leetcode.com/problems/valid-anagram/"/>
-    <hyperlink ref="F38" r:id="rId6" location="" tooltip="" display="https://leetcode.com/problems/majority-element/"/>
-    <hyperlink ref="E40" r:id="rId7" location="" tooltip="" display="https://leetcode.com/problems/build-array-from-permutation/"/>
-    <hyperlink ref="E41" r:id="rId8" location="" tooltip="" display="https://leetcode.com/problems/valid-palindrome/"/>
-    <hyperlink ref="F41" r:id="rId9" location="" tooltip="" display="https://leetcode.com/problems/two-sum-ii-input-array-is-sorted/"/>
-    <hyperlink ref="E42" r:id="rId10" location="" tooltip="" display="https://leetcode.com/problems/build-array-from-permutation/"/>
-    <hyperlink ref="F42" r:id="rId11" location="" tooltip="" display="https://leetcode.com/problems/running-sum-of-1d-array/"/>
-    <hyperlink ref="E43" r:id="rId12" location="" tooltip="" display="https://leetcode.com/problems/valid-palindrome/"/>
-    <hyperlink ref="F43" r:id="rId13" location="" tooltip="" display="https://leetcode.com/problems/move-zeroes/"/>
-    <hyperlink ref="E44" r:id="rId14" location="" tooltip="" display="https://leetcode.com/problems/two-sum-ii-input-array-is-sorted/"/>
-    <hyperlink ref="F44" r:id="rId15" location="" tooltip="" display="https://leetcode.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="E45" r:id="rId16" location="" tooltip="" display="https://leetcode.com/problems/maximum-average-subarray-i/"/>
-    <hyperlink ref="F46" r:id="rId17" location="" tooltip="" display="https://leetcode.com/problems/minimum-size-subarray-sum/"/>
-    <hyperlink ref="E48" r:id="rId18" location="" tooltip="" display="https://leetcode.com/problems/maximum-average-subarray-i/"/>
-    <hyperlink ref="F48" r:id="rId19" location="" tooltip="" display="https://leetcode.com/problems/maximum-number-of-vowels-in-a-substring-of-given-length/"/>
-    <hyperlink ref="E49" r:id="rId20" location="" tooltip="" display="https://leetcode.com/problems/minimum-size-subarray-sum/"/>
-    <hyperlink ref="F49" r:id="rId21" location="" tooltip="" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/"/>
-    <hyperlink ref="E50" r:id="rId22" location="" tooltip="" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/"/>
-    <hyperlink ref="F50" r:id="rId23" location="" tooltip="" display="https://leetcode.com/problems/longest-repeating-character-replacement/"/>
-    <hyperlink ref="E51" r:id="rId24" location="" tooltip="" display="https://leetcode.com/problems/range-sum-query-immutable/"/>
-    <hyperlink ref="E52" r:id="rId25" location="" tooltip="" display="https://leetcode.com/problems/maximum-subarray/"/>
-    <hyperlink ref="E54" r:id="rId26" location="" tooltip="" display="https://leetcode.com/problems/range-sum-query-immutable/"/>
-    <hyperlink ref="F54" r:id="rId27" location="" tooltip="" display="https://leetcode.com/problems/subarray-sum-equals-k/"/>
-    <hyperlink ref="E55" r:id="rId28" location="" tooltip="" display="https://leetcode.com/problems/maximum-subarray/"/>
-    <hyperlink ref="F55" r:id="rId29" location="" tooltip="" display="https://leetcode.com/problems/maximum-product-subarray/"/>
-    <hyperlink ref="E56" r:id="rId30" location="" tooltip="" display="https://leetcode.com/problems/best-time-to-buy-and-sell-stock/"/>
-    <hyperlink ref="F56" r:id="rId31" location="" tooltip="" display="https://leetcode.com/problems/3sum/"/>
-    <hyperlink ref="E57" r:id="rId32" location="" tooltip="" display="https://leetcode.com/problems/reverse-string/"/>
-    <hyperlink ref="E58" r:id="rId33" location="" tooltip="" display="https://leetcode.com/problems/valid-palindrome/"/>
-    <hyperlink ref="E59" r:id="rId34" location="" tooltip="" display="https://leetcode.com/problems/valid-anagram/"/>
-    <hyperlink ref="E60" r:id="rId35" location="" tooltip="" display="https://leetcode.com/problems/reverse-string/"/>
-    <hyperlink ref="F60" r:id="rId36" location="" tooltip="" display="https://leetcode.com/problems/reverse-words-in-a-string-iii/"/>
-    <hyperlink ref="E61" r:id="rId37" location="" tooltip="" display="https://leetcode.com/problems/valid-palindrome/"/>
-    <hyperlink ref="F61" r:id="rId38" location="" tooltip="" display="https://leetcode.com/problems/valid-palindrome-ii/"/>
-    <hyperlink ref="E62" r:id="rId39" location="" tooltip="" display="https://leetcode.com/problems/valid-anagram/"/>
-    <hyperlink ref="F62" r:id="rId40" location="" tooltip="" display="https://leetcode.com/problems/ransom-note/"/>
-    <hyperlink ref="E63" r:id="rId41" location="" tooltip="" display="https://leetcode.com/problems/two-sum/"/>
-    <hyperlink ref="E64" r:id="rId42" location="" tooltip="" display="https://leetcode.com/problems/contains-duplicate/"/>
-    <hyperlink ref="E65" r:id="rId43" location="" tooltip="" display="https://leetcode.com/problems/group-anagrams/"/>
-    <hyperlink ref="E66" r:id="rId44" location="" tooltip="" display="https://leetcode.com/problems/two-sum/"/>
-    <hyperlink ref="F66" r:id="rId45" location="" tooltip="" display="https://leetcode.com/problems/majority-element/"/>
-    <hyperlink ref="E67" r:id="rId46" location="" tooltip="" display="https://leetcode.com/problems/contains-duplicate/"/>
-    <hyperlink ref="F67" r:id="rId47" location="" tooltip="" display="https://leetcode.com/problems/intersection-of-two-arrays/"/>
-    <hyperlink ref="E68" r:id="rId48" location="" tooltip="" display="https://leetcode.com/problems/group-anagrams/"/>
-    <hyperlink ref="F68" r:id="rId49" location="" tooltip="" display="https://leetcode.com/problems/top-k-frequent-elements/"/>
-    <hyperlink ref="E71" r:id="rId50" location="" tooltip="" display="https://leetcode.com/problems/middle-of-the-linked-list/"/>
-    <hyperlink ref="E72" r:id="rId51" location="" tooltip="" display="https://leetcode.com/problems/reverse-linked-list/"/>
-    <hyperlink ref="F72" r:id="rId52" location="" tooltip="" display="https://leetcode.com/problems/merge-two-sorted-lists/"/>
-    <hyperlink ref="E73" r:id="rId53" location="" tooltip="" display="https://leetcode.com/problems/middle-of-the-linked-list/"/>
-    <hyperlink ref="F73" r:id="rId54" location="" tooltip="" display="https://leetcode.com/problems/linked-list-cycle/"/>
-    <hyperlink ref="E74" r:id="rId55" location="" tooltip="" display="https://leetcode.com/problems/linked-list-cycle/"/>
-    <hyperlink ref="F74" r:id="rId56" location="" tooltip="" display="https://leetcode.com/problems/palindrome-linked-list/"/>
-    <hyperlink ref="E77" r:id="rId57" location="" tooltip="" display="https://leetcode.com/problems/next-greater-element-i/"/>
-    <hyperlink ref="E78" r:id="rId58" location="" tooltip="" display="https://leetcode.com/problems/valid-parentheses/"/>
-    <hyperlink ref="F78" r:id="rId59" location="" tooltip="" display="https://leetcode.com/problems/baseball-game/"/>
-    <hyperlink ref="E79" r:id="rId60" location="" tooltip="" display="https://leetcode.com/problems/next-greater-element-i/"/>
-    <hyperlink ref="F79" r:id="rId61" location="" tooltip="" display="https://leetcode.com/problems/daily-temperatures/"/>
-    <hyperlink ref="E80" r:id="rId62" location="" tooltip="" display="https://leetcode.com/problems/daily-temperatures/"/>
-    <hyperlink ref="F80" r:id="rId63" location="" tooltip="" display="https://leetcode.com/problems/largest-rectangle-in-histogram/"/>
-    <hyperlink ref="E83" r:id="rId64" location="" tooltip="" display="https://leetcode.com/problems/number-of-recent-calls/"/>
-    <hyperlink ref="E84" r:id="rId65" location="" tooltip="" display="https://leetcode.com/problems/number-of-recent-calls/"/>
-    <hyperlink ref="F84" r:id="rId66" location="" tooltip="" display="https://leetcode.com/problems/implement-stack-using-queues/"/>
-    <hyperlink ref="E85" r:id="rId67" location="" tooltip="" display="https://leetcode.com/problems/sliding-window-maximum/"/>
-    <hyperlink ref="E86" r:id="rId68" location="" tooltip="" display="https://leetcode.com/problems/dota2-senate/"/>
-    <hyperlink ref="E88" r:id="rId69" location="" tooltip="" display="https://leetcode.com/problems/fibonacci-number/"/>
-    <hyperlink ref="E89" r:id="rId70" location="" tooltip="" display="https://leetcode.com/problems/climbing-stairs/"/>
-    <hyperlink ref="E90" r:id="rId71" location="" tooltip="" display="https://leetcode.com/problems/fibonacci-number/"/>
-    <hyperlink ref="F90" r:id="rId72" location="" tooltip="" display="https://leetcode.com/problems/power-of-two/"/>
-    <hyperlink ref="E91" r:id="rId73" location="" tooltip="" display="https://leetcode.com/problems/power-of-two/"/>
-    <hyperlink ref="F91" r:id="rId74" location="" tooltip="" display="https://leetcode.com/problems/powx-n/"/>
-    <hyperlink ref="E92" r:id="rId75" location="" tooltip="" display="https://leetcode.com/problems/climbing-stairs/"/>
-    <hyperlink ref="E94" r:id="rId76" location="" tooltip="" display="https://leetcode.com/problems/subsets/"/>
-    <hyperlink ref="E95" r:id="rId77" location="" tooltip="" display="https://leetcode.com/problems/combination-sum/"/>
-    <hyperlink ref="E96" r:id="rId78" location="" tooltip="" display="https://leetcode.com/problems/subsets/"/>
-    <hyperlink ref="F96" r:id="rId79" location="" tooltip="" display="https://leetcode.com/problems/subsets-ii/"/>
-    <hyperlink ref="E97" r:id="rId80" location="" tooltip="" display="https://leetcode.com/problems/combination-sum/"/>
-    <hyperlink ref="F97" r:id="rId81" location="" tooltip="" display="https://leetcode.com/problems/combinations/"/>
-    <hyperlink ref="E98" r:id="rId82" location="" tooltip="" display="https://leetcode.com/problems/permutations/"/>
-    <hyperlink ref="F98" r:id="rId83" location="" tooltip="" display="https://leetcode.com/problems/palindrome-partitioning/"/>
-    <hyperlink ref="E100" r:id="rId84" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-preorder-traversal/"/>
-    <hyperlink ref="E101" r:id="rId85" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-level-order-traversal/"/>
-    <hyperlink ref="E102" r:id="rId86" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-preorder-traversal/"/>
-    <hyperlink ref="F102" r:id="rId87" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-inorder-traversal/"/>
-    <hyperlink ref="E103" r:id="rId88" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-inorder-traversal/"/>
-    <hyperlink ref="F103" r:id="rId89" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-postorder-traversal/"/>
-    <hyperlink ref="E104" r:id="rId90" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-level-order-traversal/"/>
-    <hyperlink ref="F104" r:id="rId91" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-zigzag-level-order-traversal/"/>
-    <hyperlink ref="E105" r:id="rId92" location="" tooltip="" display="https://leetcode.com/problems/maximum-depth-of-binary-tree/"/>
-    <hyperlink ref="E106" r:id="rId93" location="" tooltip="" display="https://leetcode.com/problems/search-in-a-binary-search-tree/"/>
-    <hyperlink ref="E107" r:id="rId94" location="" tooltip="" display="https://leetcode.com/problems/validate-binary-search-tree/"/>
-    <hyperlink ref="E108" r:id="rId95" location="" tooltip="" display="https://leetcode.com/problems/maximum-depth-of-binary-tree/"/>
-    <hyperlink ref="F108" r:id="rId96" location="" tooltip="" display="https://leetcode.com/problems/diameter-of-binary-tree/"/>
-    <hyperlink ref="E109" r:id="rId97" location="" tooltip="" display="https://leetcode.com/problems/search-in-a-binary-search-tree/"/>
-    <hyperlink ref="F109" r:id="rId98" location="" tooltip="" display="https://leetcode.com/problems/validate-binary-search-tree/"/>
-    <hyperlink ref="E110" r:id="rId99" location="" tooltip="" display="https://leetcode.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
-    <hyperlink ref="F110" r:id="rId100" location="" tooltip="" display="https://leetcode.com/problems/path-sum/"/>
-    <hyperlink ref="E113" r:id="rId101" location="" tooltip="" display="https://leetcode.com/problems/find-if-path-exists-in-graph/"/>
-    <hyperlink ref="E114" r:id="rId102" location="" tooltip="" display="https://leetcode.com/problems/find-if-path-exists-in-graph/"/>
-    <hyperlink ref="F114" r:id="rId103" location="" tooltip="" display="https://leetcode.com/problems/keys-and-rooms/"/>
-    <hyperlink ref="E115" r:id="rId104" location="" tooltip="" display="https://leetcode.com/problems/keys-and-rooms/"/>
-    <hyperlink ref="E116" r:id="rId105" location="" tooltip="" display="https://leetcode.com/problems/number-of-provinces/"/>
-    <hyperlink ref="E117" r:id="rId106" location="" tooltip="" display="https://leetcode.com/problems/number-of-islands/"/>
-    <hyperlink ref="E118" r:id="rId107" location="" tooltip="" display="https://leetcode.com/problems/rotting-oranges/"/>
-    <hyperlink ref="E119" r:id="rId108" location="" tooltip="" display="https://leetcode.com/problems/course-schedule/"/>
-    <hyperlink ref="E120" r:id="rId109" location="" tooltip="" display="https://leetcode.com/problems/number-of-islands/"/>
-    <hyperlink ref="F120" r:id="rId110" location="" tooltip="" display="https://leetcode.com/problems/max-area-of-island/"/>
-    <hyperlink ref="E121" r:id="rId111" location="" tooltip="" display="https://leetcode.com/problems/rotting-oranges/"/>
-    <hyperlink ref="F121" r:id="rId112" location="" tooltip="" display="https://leetcode.com/problems/01-matrix/"/>
-    <hyperlink ref="E122" r:id="rId113" location="" tooltip="" display="https://leetcode.com/problems/course-schedule/"/>
-    <hyperlink ref="F122" r:id="rId114" location="" tooltip="" display="https://leetcode.com/problems/course-schedule-ii/"/>
-    <hyperlink ref="E125" r:id="rId115" location="" tooltip="" display="https://leetcode.com/problems/kth-largest-element-in-an-array/"/>
-    <hyperlink ref="E126" r:id="rId116" location="" tooltip="" display="https://leetcode.com/problems/kth-largest-element-in-a-stream/"/>
-    <hyperlink ref="F126" r:id="rId117" location="" tooltip="" display="https://leetcode.com/problems/last-stone-weight/"/>
-    <hyperlink ref="E127" r:id="rId118" location="" tooltip="" display="https://leetcode.com/problems/kth-largest-element-in-an-array/"/>
-    <hyperlink ref="F127" r:id="rId119" location="" tooltip="" display="https://leetcode.com/problems/top-k-frequent-elements/"/>
-    <hyperlink ref="E128" r:id="rId120" location="" tooltip="" display="https://leetcode.com/problems/top-k-frequent-elements/"/>
-    <hyperlink ref="F128" r:id="rId121" location="" tooltip="" display="https://leetcode.com/problems/k-closest-points-to-origin/"/>
-    <hyperlink ref="E129" r:id="rId122" location="" tooltip="" display="https://leetcode.com/problems/binary-search/"/>
-    <hyperlink ref="E131" r:id="rId123" location="" tooltip="" display="https://leetcode.com/problems/koko-eating-bananas/"/>
-    <hyperlink ref="E132" r:id="rId124" location="" tooltip="" display="https://leetcode.com/problems/binary-search/"/>
-    <hyperlink ref="F132" r:id="rId125" location="" tooltip="" display="https://leetcode.com/problems/search-insert-position/"/>
-    <hyperlink ref="E133" r:id="rId126" location="" tooltip="" display="https://leetcode.com/problems/search-insert-position/"/>
-    <hyperlink ref="F133" r:id="rId127" location="" tooltip="" display="https://leetcode.com/problems/find-first-and-last-position-of-element-in-sorted-array/"/>
-    <hyperlink ref="E134" r:id="rId128" location="" tooltip="" display="https://leetcode.com/problems/koko-eating-bananas/"/>
-    <hyperlink ref="F134" r:id="rId129" location="" tooltip="" display="https://leetcode.com/problems/capacity-to-ship-packages-within-d-days/"/>
-    <hyperlink ref="E135" r:id="rId130" location="" tooltip="" display="https://leetcode.com/problems/assign-cookies/"/>
-    <hyperlink ref="E136" r:id="rId131" location="" tooltip="" display="https://leetcode.com/problems/can-place-flowers/"/>
-    <hyperlink ref="E137" r:id="rId132" location="" tooltip="" display="https://leetcode.com/problems/lemonade-change/"/>
-    <hyperlink ref="E138" r:id="rId133" location="" tooltip="" display="https://leetcode.com/problems/assign-cookies/"/>
-    <hyperlink ref="F138" r:id="rId134" location="" tooltip="" display="https://leetcode.com/problems/can-place-flowers/"/>
-    <hyperlink ref="E139" r:id="rId135" location="" tooltip="" display="https://leetcode.com/problems/lemonade-change/"/>
-    <hyperlink ref="F139" r:id="rId136" location="" tooltip="" display="https://leetcode.com/problems/jump-game/"/>
-    <hyperlink ref="E140" r:id="rId137" location="" tooltip="" display="https://leetcode.com/problems/jump-game/"/>
-    <hyperlink ref="F140" r:id="rId138" location="" tooltip="" display="https://leetcode.com/problems/minimum-number-of-arrows-to-burst-balloons/"/>
-    <hyperlink ref="E141" r:id="rId139" location="" tooltip="" display="https://leetcode.com/problems/fibonacci-number/"/>
-    <hyperlink ref="E143" r:id="rId140" location="" tooltip="" display="https://leetcode.com/problems/climbing-stairs/"/>
-    <hyperlink ref="E144" r:id="rId141" location="" tooltip="" display="https://leetcode.com/problems/fibonacci-number/"/>
-    <hyperlink ref="F144" r:id="rId142" location="" tooltip="" display="https://leetcode.com/problems/n-th-tribonacci-number/"/>
-    <hyperlink ref="E145" r:id="rId143" location="" tooltip="" display="https://leetcode.com/problems/climbing-stairs/"/>
-    <hyperlink ref="F145" r:id="rId144" location="" tooltip="" display="https://leetcode.com/problems/min-cost-climbing-stairs/"/>
-    <hyperlink ref="E146" r:id="rId145" location="" tooltip="" display="https://leetcode.com/problems/min-cost-climbing-stairs/"/>
-    <hyperlink ref="E147" r:id="rId146" location="" tooltip="" display="https://leetcode.com/problems/house-robber/"/>
-    <hyperlink ref="E149" r:id="rId147" location="" tooltip="" display="https://leetcode.com/problems/coin-change/"/>
-    <hyperlink ref="E150" r:id="rId148" location="" tooltip="" display="https://leetcode.com/problems/house-robber/"/>
-    <hyperlink ref="F150" r:id="rId149" location="" tooltip="" display="https://leetcode.com/problems/house-robber-ii/"/>
-    <hyperlink ref="E151" r:id="rId150" location="" tooltip="" display="https://leetcode.com/problems/house-robber-ii/"/>
-    <hyperlink ref="F151" r:id="rId151" location="" tooltip="" display="https://leetcode.com/problems/delete-and-earn/"/>
-    <hyperlink ref="E152" r:id="rId152" location="" tooltip="" display="https://leetcode.com/problems/coin-change/"/>
-    <hyperlink ref="F152" r:id="rId153" location="" tooltip="" display="https://leetcode.com/problems/coin-change-ii/"/>
-    <hyperlink ref="E153" r:id="rId154" location="" tooltip="" display="https://leetcode.com/problems/unique-paths/"/>
-    <hyperlink ref="E154" r:id="rId155" location="" tooltip="" display="https://leetcode.com/problems/minimum-path-sum/"/>
-    <hyperlink ref="E155" r:id="rId156" location="" tooltip="" display="https://leetcode.com/problems/unique-paths-ii/"/>
-    <hyperlink ref="E156" r:id="rId157" location="" tooltip="" display="https://leetcode.com/problems/unique-paths/"/>
-    <hyperlink ref="F156" r:id="rId158" location="" tooltip="" display="https://leetcode.com/problems/unique-paths-ii/"/>
-    <hyperlink ref="E157" r:id="rId159" location="" tooltip="" display="https://leetcode.com/problems/minimum-path-sum/"/>
-    <hyperlink ref="F157" r:id="rId160" location="" tooltip="" display="https://leetcode.com/problems/minimum-falling-path-sum/"/>
-    <hyperlink ref="E159" r:id="rId161" location="" tooltip="" display="https://leetcode.com/problems/longest-common-subsequence/"/>
-    <hyperlink ref="E160" r:id="rId162" location="" tooltip="" display="https://leetcode.com/problems/edit-distance/"/>
-    <hyperlink ref="E161" r:id="rId163" location="" tooltip="" display="https://leetcode.com/problems/partition-equal-subset-sum/"/>
-    <hyperlink ref="E162" r:id="rId164" location="" tooltip="" display="https://leetcode.com/problems/longest-common-subsequence/"/>
-    <hyperlink ref="F162" r:id="rId165" location="" tooltip="" display="https://leetcode.com/problems/delete-operation-for-two-strings/"/>
-    <hyperlink ref="E163" r:id="rId166" location="" tooltip="" display="https://leetcode.com/problems/partition-equal-subset-sum/"/>
-    <hyperlink ref="F163" r:id="rId167" location="" tooltip="" display="https://leetcode.com/problems/target-sum/"/>
-    <hyperlink ref="F165" r:id="rId168" location="" tooltip="" display="https://sqlbolt.com/lesson/select_queries_introduction"/>
-    <hyperlink ref="F166" r:id="rId169" location="" tooltip="" display="https://sqlbolt.com/lesson/querying_all_the_things"/>
-    <hyperlink ref="E168" r:id="rId170" location="" tooltip="" display="https://leetcode.com/problems/big-countries/"/>
-    <hyperlink ref="F168" r:id="rId171" location="" tooltip="" display="https://leetcode.com/problems/recyclable-and-low-fat-products/"/>
-    <hyperlink ref="E169" r:id="rId172" location="" tooltip="" display="https://leetcode.com/problems/recyclable-and-low-fat-products/"/>
-    <hyperlink ref="F169" r:id="rId173" location="" tooltip="" display="https://leetcode.com/problems/find-customer-referee/"/>
-    <hyperlink ref="E170" r:id="rId174" location="" tooltip="" display="https://leetcode.com/problems/classes-more-than-5-students/"/>
-    <hyperlink ref="F171" r:id="rId175" location="" tooltip="" display="https://sqlbolt.com/lesson/multi_table_queries_with_joins"/>
-    <hyperlink ref="E174" r:id="rId176" location="" tooltip="" display="https://leetcode.com/problems/replace-employee-id-with-the-unique-identifier/"/>
-    <hyperlink ref="F174" r:id="rId177" location="" tooltip="" display="https://leetcode.com/problems/product-sales-analysis-i/"/>
-    <hyperlink ref="E175" r:id="rId178" location="" tooltip="" display="https://leetcode.com/problems/customers-who-never-order/"/>
-    <hyperlink ref="F175" r:id="rId179" location="" tooltip="" display="https://leetcode.com/problems/customer-who-visited-but-did-not-make-any-transactions/"/>
-    <hyperlink ref="E176" r:id="rId180" location="" tooltip="" display="https://leetcode.com/problems/employee-bonus/"/>
-    <hyperlink ref="E180" r:id="rId181" location="" tooltip="" display="https://leetcode.com/problems/rank-scores/"/>
-    <hyperlink ref="F180" r:id="rId182" location="" tooltip="" display="https://leetcode.com/problems/second-highest-salary/"/>
-    <hyperlink ref="E181" r:id="rId183" location="" tooltip="" display="https://leetcode.com/problems/department-highest-salary/"/>
+    <hyperlink ref="F36" r:id="rId1" location="" tooltip="" display="https://leetcode.com/problems/contains-duplicate/"/>
+    <hyperlink ref="E37" r:id="rId2" location="" tooltip="" display="https://leetcode.com/problems/contains-duplicate/"/>
+    <hyperlink ref="E40" r:id="rId3" location="" tooltip="" display="https://leetcode.com/problems/build-array-from-permutation/"/>
+    <hyperlink ref="F41" r:id="rId4" location="" tooltip="" display="https://leetcode.com/problems/two-sum-ii-input-array-is-sorted/"/>
+    <hyperlink ref="E42" r:id="rId5" location="" tooltip="" display="https://leetcode.com/problems/build-array-from-permutation/"/>
+    <hyperlink ref="F42" r:id="rId6" location="" tooltip="" display="https://leetcode.com/problems/running-sum-of-1d-array/"/>
+    <hyperlink ref="F43" r:id="rId7" location="" tooltip="" display="https://leetcode.com/problems/move-zeroes/"/>
+    <hyperlink ref="E44" r:id="rId8" location="" tooltip="" display="https://leetcode.com/problems/two-sum-ii-input-array-is-sorted/"/>
+    <hyperlink ref="F44" r:id="rId9" location="" tooltip="" display="https://leetcode.com/problems/remove-duplicates-from-sorted-array/"/>
+    <hyperlink ref="E45" r:id="rId10" location="" tooltip="" display="https://leetcode.com/problems/maximum-average-subarray-i/"/>
+    <hyperlink ref="F46" r:id="rId11" location="" tooltip="" display="https://leetcode.com/problems/minimum-size-subarray-sum/"/>
+    <hyperlink ref="E48" r:id="rId12" location="" tooltip="" display="https://leetcode.com/problems/maximum-average-subarray-i/"/>
+    <hyperlink ref="F48" r:id="rId13" location="" tooltip="" display="https://leetcode.com/problems/maximum-number-of-vowels-in-a-substring-of-given-length/"/>
+    <hyperlink ref="E49" r:id="rId14" location="" tooltip="" display="https://leetcode.com/problems/minimum-size-subarray-sum/"/>
+    <hyperlink ref="F49" r:id="rId15" location="" tooltip="" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/"/>
+    <hyperlink ref="E50" r:id="rId16" location="" tooltip="" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/"/>
+    <hyperlink ref="F50" r:id="rId17" location="" tooltip="" display="https://leetcode.com/problems/longest-repeating-character-replacement/"/>
+    <hyperlink ref="E51" r:id="rId18" location="" tooltip="" display="https://leetcode.com/problems/range-sum-query-immutable/"/>
+    <hyperlink ref="E52" r:id="rId19" location="" tooltip="" display="https://leetcode.com/problems/maximum-subarray/"/>
+    <hyperlink ref="E54" r:id="rId20" location="" tooltip="" display="https://leetcode.com/problems/range-sum-query-immutable/"/>
+    <hyperlink ref="F54" r:id="rId21" location="" tooltip="" display="https://leetcode.com/problems/subarray-sum-equals-k/"/>
+    <hyperlink ref="E55" r:id="rId22" location="" tooltip="" display="https://leetcode.com/problems/maximum-subarray/"/>
+    <hyperlink ref="F55" r:id="rId23" location="" tooltip="" display="https://leetcode.com/problems/maximum-product-subarray/"/>
+    <hyperlink ref="E56" r:id="rId24" location="" tooltip="" display="https://leetcode.com/problems/best-time-to-buy-and-sell-stock/"/>
+    <hyperlink ref="F56" r:id="rId25" location="" tooltip="" display="https://leetcode.com/problems/3sum/"/>
+    <hyperlink ref="E57" r:id="rId26" location="" tooltip="" display="https://leetcode.com/problems/reverse-string/"/>
+    <hyperlink ref="E58" r:id="rId27" location="" tooltip="" display="https://leetcode.com/problems/valid-palindrome/"/>
+    <hyperlink ref="E59" r:id="rId28" location="" tooltip="" display="https://leetcode.com/problems/valid-anagram/"/>
+    <hyperlink ref="E60" r:id="rId29" location="" tooltip="" display="https://leetcode.com/problems/reverse-string/"/>
+    <hyperlink ref="F60" r:id="rId30" location="" tooltip="" display="https://leetcode.com/problems/reverse-words-in-a-string-iii/"/>
+    <hyperlink ref="E61" r:id="rId31" location="" tooltip="" display="https://leetcode.com/problems/valid-palindrome/"/>
+    <hyperlink ref="F61" r:id="rId32" location="" tooltip="" display="https://leetcode.com/problems/valid-palindrome-ii/"/>
+    <hyperlink ref="E62" r:id="rId33" location="" tooltip="" display="https://leetcode.com/problems/valid-anagram/"/>
+    <hyperlink ref="F62" r:id="rId34" location="" tooltip="" display="https://leetcode.com/problems/ransom-note/"/>
+    <hyperlink ref="E63" r:id="rId35" location="" tooltip="" display="https://leetcode.com/problems/two-sum/"/>
+    <hyperlink ref="E65" r:id="rId36" location="" tooltip="" display="https://leetcode.com/problems/group-anagrams/"/>
+    <hyperlink ref="E66" r:id="rId37" location="" tooltip="" display="https://leetcode.com/problems/two-sum/"/>
+    <hyperlink ref="F66" r:id="rId38" location="" tooltip="" display="https://leetcode.com/problems/majority-element/"/>
+    <hyperlink ref="F67" r:id="rId39" location="" tooltip="" display="https://leetcode.com/problems/intersection-of-two-arrays/"/>
+    <hyperlink ref="E68" r:id="rId40" location="" tooltip="" display="https://leetcode.com/problems/group-anagrams/"/>
+    <hyperlink ref="E71" r:id="rId41" location="" tooltip="" display="https://leetcode.com/problems/middle-of-the-linked-list/"/>
+    <hyperlink ref="E72" r:id="rId42" location="" tooltip="" display="https://leetcode.com/problems/reverse-linked-list/"/>
+    <hyperlink ref="F72" r:id="rId43" location="" tooltip="" display="https://leetcode.com/problems/merge-two-sorted-lists/"/>
+    <hyperlink ref="E73" r:id="rId44" location="" tooltip="" display="https://leetcode.com/problems/middle-of-the-linked-list/"/>
+    <hyperlink ref="F73" r:id="rId45" location="" tooltip="" display="https://leetcode.com/problems/linked-list-cycle/"/>
+    <hyperlink ref="E74" r:id="rId46" location="" tooltip="" display="https://leetcode.com/problems/linked-list-cycle/"/>
+    <hyperlink ref="F74" r:id="rId47" location="" tooltip="" display="https://leetcode.com/problems/palindrome-linked-list/"/>
+    <hyperlink ref="E77" r:id="rId48" location="" tooltip="" display="https://leetcode.com/problems/next-greater-element-i/"/>
+    <hyperlink ref="E78" r:id="rId49" location="" tooltip="" display="https://leetcode.com/problems/valid-parentheses/"/>
+    <hyperlink ref="F78" r:id="rId50" location="" tooltip="" display="https://leetcode.com/problems/baseball-game/"/>
+    <hyperlink ref="E79" r:id="rId51" location="" tooltip="" display="https://leetcode.com/problems/next-greater-element-i/"/>
+    <hyperlink ref="F79" r:id="rId52" location="" tooltip="" display="https://leetcode.com/problems/daily-temperatures/"/>
+    <hyperlink ref="E80" r:id="rId53" location="" tooltip="" display="https://leetcode.com/problems/daily-temperatures/"/>
+    <hyperlink ref="F80" r:id="rId54" location="" tooltip="" display="https://leetcode.com/problems/largest-rectangle-in-histogram/"/>
+    <hyperlink ref="E83" r:id="rId55" location="" tooltip="" display="https://leetcode.com/problems/number-of-recent-calls/"/>
+    <hyperlink ref="E84" r:id="rId56" location="" tooltip="" display="https://leetcode.com/problems/number-of-recent-calls/"/>
+    <hyperlink ref="F84" r:id="rId57" location="" tooltip="" display="https://leetcode.com/problems/implement-stack-using-queues/"/>
+    <hyperlink ref="E85" r:id="rId58" location="" tooltip="" display="https://leetcode.com/problems/sliding-window-maximum/"/>
+    <hyperlink ref="E86" r:id="rId59" location="" tooltip="" display="https://leetcode.com/problems/dota2-senate/"/>
+    <hyperlink ref="E88" r:id="rId60" location="" tooltip="" display="https://leetcode.com/problems/fibonacci-number/"/>
+    <hyperlink ref="E90" r:id="rId61" location="" tooltip="" display="https://leetcode.com/problems/fibonacci-number/"/>
+    <hyperlink ref="F90" r:id="rId62" location="" tooltip="" display="https://leetcode.com/problems/power-of-two/"/>
+    <hyperlink ref="E91" r:id="rId63" location="" tooltip="" display="https://leetcode.com/problems/power-of-two/"/>
+    <hyperlink ref="F91" r:id="rId64" location="" tooltip="" display="https://leetcode.com/problems/powx-n/"/>
+    <hyperlink ref="E94" r:id="rId65" location="" tooltip="" display="https://leetcode.com/problems/subsets/"/>
+    <hyperlink ref="E95" r:id="rId66" location="" tooltip="" display="https://leetcode.com/problems/combination-sum/"/>
+    <hyperlink ref="E96" r:id="rId67" location="" tooltip="" display="https://leetcode.com/problems/subsets/"/>
+    <hyperlink ref="F96" r:id="rId68" location="" tooltip="" display="https://leetcode.com/problems/subsets-ii/"/>
+    <hyperlink ref="E97" r:id="rId69" location="" tooltip="" display="https://leetcode.com/problems/combination-sum/"/>
+    <hyperlink ref="F97" r:id="rId70" location="" tooltip="" display="https://leetcode.com/problems/combinations/"/>
+    <hyperlink ref="E98" r:id="rId71" location="" tooltip="" display="https://leetcode.com/problems/permutations/"/>
+    <hyperlink ref="F98" r:id="rId72" location="" tooltip="" display="https://leetcode.com/problems/palindrome-partitioning/"/>
+    <hyperlink ref="E100" r:id="rId73" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-preorder-traversal/"/>
+    <hyperlink ref="E101" r:id="rId74" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-level-order-traversal/"/>
+    <hyperlink ref="E102" r:id="rId75" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-preorder-traversal/"/>
+    <hyperlink ref="F102" r:id="rId76" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-inorder-traversal/"/>
+    <hyperlink ref="E103" r:id="rId77" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-inorder-traversal/"/>
+    <hyperlink ref="F103" r:id="rId78" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-postorder-traversal/"/>
+    <hyperlink ref="E104" r:id="rId79" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-level-order-traversal/"/>
+    <hyperlink ref="F104" r:id="rId80" location="" tooltip="" display="https://leetcode.com/problems/binary-tree-zigzag-level-order-traversal/"/>
+    <hyperlink ref="E105" r:id="rId81" location="" tooltip="" display="https://leetcode.com/problems/maximum-depth-of-binary-tree/"/>
+    <hyperlink ref="E106" r:id="rId82" location="" tooltip="" display="https://leetcode.com/problems/search-in-a-binary-search-tree/"/>
+    <hyperlink ref="E107" r:id="rId83" location="" tooltip="" display="https://leetcode.com/problems/validate-binary-search-tree/"/>
+    <hyperlink ref="E108" r:id="rId84" location="" tooltip="" display="https://leetcode.com/problems/maximum-depth-of-binary-tree/"/>
+    <hyperlink ref="F108" r:id="rId85" location="" tooltip="" display="https://leetcode.com/problems/diameter-of-binary-tree/"/>
+    <hyperlink ref="E109" r:id="rId86" location="" tooltip="" display="https://leetcode.com/problems/search-in-a-binary-search-tree/"/>
+    <hyperlink ref="F109" r:id="rId87" location="" tooltip="" display="https://leetcode.com/problems/validate-binary-search-tree/"/>
+    <hyperlink ref="E110" r:id="rId88" location="" tooltip="" display="https://leetcode.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
+    <hyperlink ref="F110" r:id="rId89" location="" tooltip="" display="https://leetcode.com/problems/path-sum/"/>
+    <hyperlink ref="E113" r:id="rId90" location="" tooltip="" display="https://leetcode.com/problems/find-if-path-exists-in-graph/"/>
+    <hyperlink ref="E114" r:id="rId91" location="" tooltip="" display="https://leetcode.com/problems/find-if-path-exists-in-graph/"/>
+    <hyperlink ref="F114" r:id="rId92" location="" tooltip="" display="https://leetcode.com/problems/keys-and-rooms/"/>
+    <hyperlink ref="E115" r:id="rId93" location="" tooltip="" display="https://leetcode.com/problems/keys-and-rooms/"/>
+    <hyperlink ref="E116" r:id="rId94" location="" tooltip="" display="https://leetcode.com/problems/number-of-provinces/"/>
+    <hyperlink ref="E117" r:id="rId95" location="" tooltip="" display="https://leetcode.com/problems/number-of-islands/"/>
+    <hyperlink ref="E118" r:id="rId96" location="" tooltip="" display="https://leetcode.com/problems/rotting-oranges/"/>
+    <hyperlink ref="E119" r:id="rId97" location="" tooltip="" display="https://leetcode.com/problems/course-schedule/"/>
+    <hyperlink ref="E120" r:id="rId98" location="" tooltip="" display="https://leetcode.com/problems/number-of-islands/"/>
+    <hyperlink ref="F120" r:id="rId99" location="" tooltip="" display="https://leetcode.com/problems/max-area-of-island/"/>
+    <hyperlink ref="E121" r:id="rId100" location="" tooltip="" display="https://leetcode.com/problems/rotting-oranges/"/>
+    <hyperlink ref="F121" r:id="rId101" location="" tooltip="" display="https://leetcode.com/problems/01-matrix/"/>
+    <hyperlink ref="E122" r:id="rId102" location="" tooltip="" display="https://leetcode.com/problems/course-schedule/"/>
+    <hyperlink ref="F122" r:id="rId103" location="" tooltip="" display="https://leetcode.com/problems/course-schedule-ii/"/>
+    <hyperlink ref="E125" r:id="rId104" location="" tooltip="" display="https://leetcode.com/problems/kth-largest-element-in-an-array/"/>
+    <hyperlink ref="E126" r:id="rId105" location="" tooltip="" display="https://leetcode.com/problems/kth-largest-element-in-a-stream/"/>
+    <hyperlink ref="F126" r:id="rId106" location="" tooltip="" display="https://leetcode.com/problems/last-stone-weight/"/>
+    <hyperlink ref="E127" r:id="rId107" location="" tooltip="" display="https://leetcode.com/problems/kth-largest-element-in-an-array/"/>
+    <hyperlink ref="F127" r:id="rId108" location="" tooltip="" display="https://leetcode.com/problems/top-k-frequent-elements/"/>
+    <hyperlink ref="E128" r:id="rId109" location="" tooltip="" display="https://leetcode.com/problems/top-k-frequent-elements/"/>
+    <hyperlink ref="F128" r:id="rId110" location="" tooltip="" display="https://leetcode.com/problems/k-closest-points-to-origin/"/>
+    <hyperlink ref="E129" r:id="rId111" location="" tooltip="" display="https://leetcode.com/problems/binary-search/"/>
+    <hyperlink ref="E131" r:id="rId112" location="" tooltip="" display="https://leetcode.com/problems/koko-eating-bananas/"/>
+    <hyperlink ref="E132" r:id="rId113" location="" tooltip="" display="https://leetcode.com/problems/binary-search/"/>
+    <hyperlink ref="F132" r:id="rId114" location="" tooltip="" display="https://leetcode.com/problems/search-insert-position/"/>
+    <hyperlink ref="E133" r:id="rId115" location="" tooltip="" display="https://leetcode.com/problems/search-insert-position/"/>
+    <hyperlink ref="F133" r:id="rId116" location="" tooltip="" display="https://leetcode.com/problems/find-first-and-last-position-of-element-in-sorted-array/"/>
+    <hyperlink ref="E134" r:id="rId117" location="" tooltip="" display="https://leetcode.com/problems/koko-eating-bananas/"/>
+    <hyperlink ref="F134" r:id="rId118" location="" tooltip="" display="https://leetcode.com/problems/capacity-to-ship-packages-within-d-days/"/>
+    <hyperlink ref="E135" r:id="rId119" location="" tooltip="" display="https://leetcode.com/problems/assign-cookies/"/>
+    <hyperlink ref="E136" r:id="rId120" location="" tooltip="" display="https://leetcode.com/problems/can-place-flowers/"/>
+    <hyperlink ref="E137" r:id="rId121" location="" tooltip="" display="https://leetcode.com/problems/lemonade-change/"/>
+    <hyperlink ref="E138" r:id="rId122" location="" tooltip="" display="https://leetcode.com/problems/assign-cookies/"/>
+    <hyperlink ref="F138" r:id="rId123" location="" tooltip="" display="https://leetcode.com/problems/can-place-flowers/"/>
+    <hyperlink ref="E139" r:id="rId124" location="" tooltip="" display="https://leetcode.com/problems/lemonade-change/"/>
+    <hyperlink ref="F139" r:id="rId125" location="" tooltip="" display="https://leetcode.com/problems/jump-game/"/>
+    <hyperlink ref="E140" r:id="rId126" location="" tooltip="" display="https://leetcode.com/problems/jump-game/"/>
+    <hyperlink ref="F140" r:id="rId127" location="" tooltip="" display="https://leetcode.com/problems/minimum-number-of-arrows-to-burst-balloons/"/>
+    <hyperlink ref="E143" r:id="rId128" location="" tooltip="" display="https://leetcode.com/problems/climbing-stairs/"/>
+    <hyperlink ref="F144" r:id="rId129" location="" tooltip="" display="https://leetcode.com/problems/n-th-tribonacci-number/"/>
+    <hyperlink ref="E145" r:id="rId130" location="" tooltip="" display="https://leetcode.com/problems/climbing-stairs/"/>
+    <hyperlink ref="F145" r:id="rId131" location="" tooltip="" display="https://leetcode.com/problems/min-cost-climbing-stairs/"/>
+    <hyperlink ref="E146" r:id="rId132" location="" tooltip="" display="https://leetcode.com/problems/min-cost-climbing-stairs/"/>
+    <hyperlink ref="E147" r:id="rId133" location="" tooltip="" display="https://leetcode.com/problems/house-robber/"/>
+    <hyperlink ref="E149" r:id="rId134" location="" tooltip="" display="https://leetcode.com/problems/coin-change/"/>
+    <hyperlink ref="E150" r:id="rId135" location="" tooltip="" display="https://leetcode.com/problems/house-robber/"/>
+    <hyperlink ref="F150" r:id="rId136" location="" tooltip="" display="https://leetcode.com/problems/house-robber-ii/"/>
+    <hyperlink ref="E151" r:id="rId137" location="" tooltip="" display="https://leetcode.com/problems/house-robber-ii/"/>
+    <hyperlink ref="F151" r:id="rId138" location="" tooltip="" display="https://leetcode.com/problems/delete-and-earn/"/>
+    <hyperlink ref="E152" r:id="rId139" location="" tooltip="" display="https://leetcode.com/problems/coin-change/"/>
+    <hyperlink ref="F152" r:id="rId140" location="" tooltip="" display="https://leetcode.com/problems/coin-change-ii/"/>
+    <hyperlink ref="E153" r:id="rId141" location="" tooltip="" display="https://leetcode.com/problems/unique-paths/"/>
+    <hyperlink ref="E154" r:id="rId142" location="" tooltip="" display="https://leetcode.com/problems/minimum-path-sum/"/>
+    <hyperlink ref="E155" r:id="rId143" location="" tooltip="" display="https://leetcode.com/problems/unique-paths-ii/"/>
+    <hyperlink ref="E156" r:id="rId144" location="" tooltip="" display="https://leetcode.com/problems/unique-paths/"/>
+    <hyperlink ref="F156" r:id="rId145" location="" tooltip="" display="https://leetcode.com/problems/unique-paths-ii/"/>
+    <hyperlink ref="E157" r:id="rId146" location="" tooltip="" display="https://leetcode.com/problems/minimum-path-sum/"/>
+    <hyperlink ref="F157" r:id="rId147" location="" tooltip="" display="https://leetcode.com/problems/minimum-falling-path-sum/"/>
+    <hyperlink ref="E159" r:id="rId148" location="" tooltip="" display="https://leetcode.com/problems/longest-common-subsequence/"/>
+    <hyperlink ref="E160" r:id="rId149" location="" tooltip="" display="https://leetcode.com/problems/edit-distance/"/>
+    <hyperlink ref="E161" r:id="rId150" location="" tooltip="" display="https://leetcode.com/problems/partition-equal-subset-sum/"/>
+    <hyperlink ref="E162" r:id="rId151" location="" tooltip="" display="https://leetcode.com/problems/longest-common-subsequence/"/>
+    <hyperlink ref="F162" r:id="rId152" location="" tooltip="" display="https://leetcode.com/problems/delete-operation-for-two-strings/"/>
+    <hyperlink ref="E163" r:id="rId153" location="" tooltip="" display="https://leetcode.com/problems/partition-equal-subset-sum/"/>
+    <hyperlink ref="F163" r:id="rId154" location="" tooltip="" display="https://leetcode.com/problems/target-sum/"/>
+    <hyperlink ref="F165" r:id="rId155" location="" tooltip="" display="https://sqlbolt.com/lesson/select_queries_introduction"/>
+    <hyperlink ref="F166" r:id="rId156" location="" tooltip="" display="https://sqlbolt.com/lesson/querying_all_the_things"/>
+    <hyperlink ref="E168" r:id="rId157" location="" tooltip="" display="https://leetcode.com/problems/big-countries/"/>
+    <hyperlink ref="F168" r:id="rId158" location="" tooltip="" display="https://leetcode.com/problems/recyclable-and-low-fat-products/"/>
+    <hyperlink ref="E169" r:id="rId159" location="" tooltip="" display="https://leetcode.com/problems/recyclable-and-low-fat-products/"/>
+    <hyperlink ref="F169" r:id="rId160" location="" tooltip="" display="https://leetcode.com/problems/find-customer-referee/"/>
+    <hyperlink ref="E170" r:id="rId161" location="" tooltip="" display="https://leetcode.com/problems/classes-more-than-5-students/"/>
+    <hyperlink ref="F171" r:id="rId162" location="" tooltip="" display="https://sqlbolt.com/lesson/multi_table_queries_with_joins"/>
+    <hyperlink ref="E174" r:id="rId163" location="" tooltip="" display="https://leetcode.com/problems/replace-employee-id-with-the-unique-identifier/"/>
+    <hyperlink ref="F174" r:id="rId164" location="" tooltip="" display="https://leetcode.com/problems/product-sales-analysis-i/"/>
+    <hyperlink ref="E175" r:id="rId165" location="" tooltip="" display="https://leetcode.com/problems/customers-who-never-order/"/>
+    <hyperlink ref="F175" r:id="rId166" location="" tooltip="" display="https://leetcode.com/problems/customer-who-visited-but-did-not-make-any-transactions/"/>
+    <hyperlink ref="E176" r:id="rId167" location="" tooltip="" display="https://leetcode.com/problems/employee-bonus/"/>
+    <hyperlink ref="E180" r:id="rId168" location="" tooltip="" display="https://leetcode.com/problems/rank-scores/"/>
+    <hyperlink ref="F180" r:id="rId169" location="" tooltip="" display="https://leetcode.com/problems/second-highest-salary/"/>
+    <hyperlink ref="E181" r:id="rId170" location="" tooltip="" display="https://leetcode.com/problems/department-highest-salary/"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
